--- a/playground/qi_changes3.xlsx
+++ b/playground/qi_changes3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\yochayc\INES\playground\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7E7B3D6-A858-43AB-B605-C3E54B8D24CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A915E263-1EA3-4FF5-B2E5-3C814F3D0336}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-1485" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="answers_missing_or_added" sheetId="2" r:id="rId1"/>
@@ -26393,7 +26393,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -26416,11 +26416,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -26431,11 +26444,72 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="7">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+      </border>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -26446,6 +26520,31 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{16EA9378-9F6E-4EA3-995F-08677E977B34}" name="Table1" displayName="Table1" ref="A1:M109" totalsRowShown="0" headerRowDxfId="0" dataDxfId="1" headerRowBorderDxfId="5" tableBorderDxfId="6">
+  <autoFilter ref="A1:M109" xr:uid="{16EA9378-9F6E-4EA3-995F-08677E977B34}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M109">
+    <sortCondition ref="G1:G109"/>
+  </sortState>
+  <tableColumns count="13">
+    <tableColumn id="1" xr3:uid="{A0A2D8CF-7DB9-4861-8A6C-435BD8EB600F}" name="שאלה"/>
+    <tableColumn id="2" xr3:uid="{C3B39996-9163-4014-88FD-175F8E7DEA8C}" name="קטגוריה"/>
+    <tableColumn id="3" xr3:uid="{28C12083-EF5D-41F6-8DBB-5DD7555B14B1}" name="סקר_קודם"/>
+    <tableColumn id="4" xr3:uid="{139AC3E3-C370-4A2C-9200-898EBC6F4BD2}" name="סקר חדש"/>
+    <tableColumn id="5" xr3:uid="{51F19EFD-9DB5-4CE3-ADFD-B4F333765A91}" name="main_change_type"/>
+    <tableColumn id="6" xr3:uid="{FC5E43A4-5BD6-4D39-A5EB-FC16446019A8}" name="secondary_change_type"/>
+    <tableColumn id="7" xr3:uid="{90DE6B2E-A0EA-4D1D-B060-D20F1442DAF1}" name="מידת שינוי"/>
+    <tableColumn id="8" xr3:uid="{28081664-80B1-403D-ABAE-2F7842495893}" name="description_diff"/>
+    <tableColumn id="9" xr3:uid="{1F5F5D8A-78B7-4DFC-961C-51CB59076FE7}" name="תיאור קודם"/>
+    <tableColumn id="10" xr3:uid="{060D7DE2-F391-4863-91B1-82B7F7BD2592}" name="תיאור חדש"/>
+    <tableColumn id="11" xr3:uid="{836A5C0E-3B24-4588-B43B-CCA131C05A0A}" name="ans_diff" dataDxfId="4"/>
+    <tableColumn id="12" xr3:uid="{6D47E09D-969A-4AD7-BFA7-8190AEA09A97}" name="לפני" dataDxfId="3"/>
+    <tableColumn id="13" xr3:uid="{910E8EE6-3EFC-4271-A46F-F1F361392F54}" name="אחרי" dataDxfId="2"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -26861,629 +26960,638 @@
   <dimension ref="A1:M109"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
+    <col min="3" max="3" width="10.6640625" customWidth="1"/>
+    <col min="4" max="4" width="10.109375" customWidth="1"/>
+    <col min="5" max="5" width="19" customWidth="1"/>
+    <col min="6" max="6" width="23.44140625" customWidth="1"/>
+    <col min="7" max="7" width="10.5546875" customWidth="1"/>
+    <col min="8" max="8" width="16.109375" customWidth="1"/>
+    <col min="9" max="10" width="11" customWidth="1"/>
     <col min="11" max="11" width="45.109375" style="3" customWidth="1"/>
+    <col min="12" max="12" width="42.88671875" style="3" customWidth="1"/>
+    <col min="13" max="13" width="45" style="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>40</v>
+        <v>69</v>
       </c>
       <c r="B2" t="s">
         <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>73</v>
+        <v>32</v>
       </c>
       <c r="D2" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="E2" t="s">
         <v>275</v>
       </c>
       <c r="G2">
-        <v>0.98</v>
+        <v>0.31</v>
       </c>
       <c r="H2" t="s">
         <v>17</v>
       </c>
       <c r="I2" t="s">
-        <v>276</v>
+        <v>332</v>
       </c>
       <c r="J2" t="s">
-        <v>276</v>
+        <v>332</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="L2" t="s">
-        <v>278</v>
-      </c>
-      <c r="M2" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="129.6" x14ac:dyDescent="0.3">
+        <v>333</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="B3" t="s">
         <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="D3" t="s">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="E3" t="s">
         <v>275</v>
       </c>
       <c r="G3">
-        <v>0.98</v>
+        <v>0.31</v>
       </c>
       <c r="H3" t="s">
         <v>17</v>
       </c>
       <c r="I3" t="s">
-        <v>276</v>
+        <v>369</v>
       </c>
       <c r="J3" t="s">
-        <v>276</v>
+        <v>369</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>280</v>
-      </c>
-      <c r="L3" t="s">
-        <v>279</v>
-      </c>
-      <c r="M3" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="374.4" x14ac:dyDescent="0.3">
+        <v>370</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>40</v>
+        <v>343</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="D4" t="s">
-        <v>30</v>
+        <v>344</v>
       </c>
       <c r="E4" t="s">
         <v>275</v>
       </c>
       <c r="G4">
-        <v>0.74</v>
+        <v>0.4</v>
       </c>
       <c r="H4" t="s">
         <v>17</v>
       </c>
       <c r="I4" t="s">
-        <v>46</v>
+        <v>345</v>
       </c>
       <c r="J4" t="s">
-        <v>46</v>
+        <v>345</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>281</v>
-      </c>
-      <c r="L4" t="s">
-        <v>282</v>
-      </c>
-      <c r="M4" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="331.2" x14ac:dyDescent="0.3">
+        <v>346</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>40</v>
+        <v>98</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>94</v>
       </c>
       <c r="C5" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E5" t="s">
         <v>275</v>
       </c>
       <c r="G5">
-        <v>0.88</v>
+        <v>0.41</v>
       </c>
       <c r="H5" t="s">
         <v>17</v>
       </c>
       <c r="I5" t="s">
-        <v>46</v>
+        <v>404</v>
       </c>
       <c r="J5" t="s">
-        <v>46</v>
+        <v>404</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>284</v>
-      </c>
-      <c r="L5" t="s">
-        <v>285</v>
-      </c>
-      <c r="M5" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="216" x14ac:dyDescent="0.3">
+        <v>405</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>47</v>
+        <v>69</v>
       </c>
       <c r="B6" t="s">
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>73</v>
+        <v>35</v>
       </c>
       <c r="D6" t="s">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="E6" t="s">
         <v>275</v>
       </c>
       <c r="G6">
-        <v>0.93</v>
+        <v>0.43</v>
       </c>
       <c r="H6" t="s">
         <v>17</v>
       </c>
       <c r="I6" t="s">
-        <v>48</v>
+        <v>336</v>
       </c>
       <c r="J6" t="s">
-        <v>48</v>
+        <v>336</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>287</v>
-      </c>
-      <c r="L6" t="s">
-        <v>288</v>
-      </c>
-      <c r="M6" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="302.39999999999998" x14ac:dyDescent="0.3">
+        <v>337</v>
+      </c>
+      <c r="L6" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="M6" s="3" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="230.4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>47</v>
+        <v>128</v>
       </c>
       <c r="B7" t="s">
-        <v>14</v>
+        <v>117</v>
       </c>
       <c r="C7" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="D7" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="E7" t="s">
         <v>275</v>
       </c>
       <c r="G7">
-        <v>0.63</v>
+        <v>0.43</v>
       </c>
       <c r="H7" t="s">
         <v>17</v>
       </c>
       <c r="I7" t="s">
-        <v>49</v>
+        <v>459</v>
       </c>
       <c r="J7" t="s">
-        <v>49</v>
+        <v>459</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>290</v>
-      </c>
-      <c r="L7" t="s">
-        <v>291</v>
-      </c>
-      <c r="M7" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+        <v>460</v>
+      </c>
+      <c r="L7" s="3" t="s">
+        <v>461</v>
+      </c>
+      <c r="M7" s="3" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>47</v>
+        <v>531</v>
       </c>
       <c r="B8" t="s">
-        <v>14</v>
+        <v>191</v>
       </c>
       <c r="C8" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="D8" t="s">
-        <v>96</v>
+        <v>51</v>
       </c>
       <c r="E8" t="s">
         <v>275</v>
       </c>
       <c r="G8">
-        <v>0.62</v>
+        <v>0.47</v>
       </c>
       <c r="H8" t="s">
         <v>17</v>
       </c>
       <c r="I8" t="s">
-        <v>293</v>
+        <v>532</v>
       </c>
       <c r="J8" t="s">
-        <v>293</v>
+        <v>532</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>294</v>
-      </c>
-      <c r="L8" t="s">
-        <v>295</v>
-      </c>
-      <c r="M8" t="s">
-        <v>296</v>
+        <v>533</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>534</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>535</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>297</v>
+        <v>536</v>
       </c>
       <c r="B9" t="s">
-        <v>14</v>
+        <v>191</v>
       </c>
       <c r="C9" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D9" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="E9" t="s">
         <v>275</v>
       </c>
       <c r="G9">
-        <v>0.6</v>
+        <v>0.47</v>
       </c>
       <c r="H9" t="s">
         <v>17</v>
       </c>
       <c r="I9" t="s">
-        <v>298</v>
+        <v>537</v>
       </c>
       <c r="J9" t="s">
-        <v>298</v>
+        <v>537</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>299</v>
-      </c>
-      <c r="L9" t="s">
-        <v>300</v>
-      </c>
-      <c r="M9" t="s">
-        <v>301</v>
+        <v>533</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>534</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>535</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>302</v>
+        <v>538</v>
       </c>
       <c r="B10" t="s">
-        <v>14</v>
+        <v>191</v>
       </c>
       <c r="C10" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D10" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="E10" t="s">
         <v>275</v>
       </c>
       <c r="G10">
-        <v>0.6</v>
+        <v>0.47</v>
       </c>
       <c r="H10" t="s">
         <v>17</v>
       </c>
       <c r="I10" t="s">
-        <v>303</v>
+        <v>539</v>
       </c>
       <c r="J10" t="s">
-        <v>303</v>
+        <v>539</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>299</v>
-      </c>
-      <c r="L10" t="s">
-        <v>300</v>
-      </c>
-      <c r="M10" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" ht="129.6" x14ac:dyDescent="0.3">
+        <v>533</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>534</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>304</v>
+        <v>152</v>
       </c>
       <c r="B11" t="s">
-        <v>14</v>
+        <v>153</v>
       </c>
       <c r="C11" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="D11" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="E11" t="s">
         <v>275</v>
       </c>
       <c r="G11">
-        <v>0.6</v>
+        <v>0.49</v>
       </c>
       <c r="H11" t="s">
         <v>17</v>
       </c>
       <c r="I11" t="s">
-        <v>305</v>
+        <v>154</v>
       </c>
       <c r="J11" t="s">
-        <v>305</v>
+        <v>154</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>299</v>
-      </c>
-      <c r="L11" t="s">
-        <v>300</v>
-      </c>
-      <c r="M11" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" ht="129.6" x14ac:dyDescent="0.3">
+        <v>503</v>
+      </c>
+      <c r="L11" s="3" t="s">
+        <v>504</v>
+      </c>
+      <c r="M11" s="3" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>306</v>
+        <v>157</v>
       </c>
       <c r="B12" t="s">
-        <v>14</v>
+        <v>153</v>
       </c>
       <c r="C12" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="D12" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="E12" t="s">
         <v>275</v>
       </c>
       <c r="G12">
-        <v>0.6</v>
+        <v>0.49</v>
       </c>
       <c r="H12" t="s">
         <v>17</v>
       </c>
       <c r="I12" t="s">
-        <v>307</v>
+        <v>158</v>
       </c>
       <c r="J12" t="s">
-        <v>307</v>
+        <v>158</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>299</v>
-      </c>
-      <c r="L12" t="s">
-        <v>300</v>
-      </c>
-      <c r="M12" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" ht="187.2" x14ac:dyDescent="0.3">
+        <v>503</v>
+      </c>
+      <c r="L12" s="3" t="s">
+        <v>504</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>55</v>
+        <v>165</v>
       </c>
       <c r="B13" t="s">
-        <v>14</v>
+        <v>153</v>
       </c>
       <c r="C13" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="D13" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="E13" t="s">
         <v>275</v>
       </c>
       <c r="G13">
-        <v>0.56999999999999995</v>
+        <v>0.49</v>
       </c>
       <c r="H13" t="s">
         <v>17</v>
       </c>
       <c r="I13" t="s">
-        <v>308</v>
+        <v>166</v>
       </c>
       <c r="J13" t="s">
-        <v>308</v>
+        <v>166</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>309</v>
-      </c>
-      <c r="L13" t="s">
-        <v>310</v>
-      </c>
-      <c r="M13" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" ht="129.6" x14ac:dyDescent="0.3">
+        <v>503</v>
+      </c>
+      <c r="L13" s="3" t="s">
+        <v>504</v>
+      </c>
+      <c r="M13" s="3" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>65</v>
+        <v>169</v>
       </c>
       <c r="B14" t="s">
-        <v>14</v>
+        <v>153</v>
       </c>
       <c r="C14" t="s">
-        <v>73</v>
+        <v>28</v>
       </c>
       <c r="D14" t="s">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="E14" t="s">
         <v>275</v>
       </c>
       <c r="G14">
-        <v>0.96</v>
+        <v>0.49</v>
       </c>
       <c r="H14" t="s">
         <v>17</v>
       </c>
       <c r="I14" t="s">
-        <v>66</v>
+        <v>170</v>
       </c>
       <c r="J14" t="s">
-        <v>66</v>
+        <v>170</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>312</v>
-      </c>
-      <c r="L14" t="s">
-        <v>313</v>
-      </c>
-      <c r="M14" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" ht="216" x14ac:dyDescent="0.3">
+        <v>503</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>504</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>67</v>
+        <v>171</v>
       </c>
       <c r="B15" t="s">
-        <v>14</v>
+        <v>153</v>
       </c>
       <c r="C15" t="s">
-        <v>73</v>
+        <v>28</v>
       </c>
       <c r="D15" t="s">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="E15" t="s">
         <v>275</v>
       </c>
       <c r="G15">
-        <v>0.98</v>
+        <v>0.49</v>
       </c>
       <c r="H15" t="s">
         <v>17</v>
       </c>
       <c r="I15" t="s">
-        <v>68</v>
+        <v>172</v>
       </c>
       <c r="J15" t="s">
-        <v>68</v>
+        <v>172</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>315</v>
-      </c>
-      <c r="L15" t="s">
-        <v>316</v>
-      </c>
-      <c r="M15" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" ht="273.60000000000002" x14ac:dyDescent="0.3">
+        <v>503</v>
+      </c>
+      <c r="L15" s="3" t="s">
+        <v>504</v>
+      </c>
+      <c r="M15" s="3" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>67</v>
+        <v>177</v>
       </c>
       <c r="B16" t="s">
-        <v>14</v>
+        <v>153</v>
       </c>
       <c r="C16" t="s">
-        <v>318</v>
+        <v>28</v>
       </c>
       <c r="D16" t="s">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="E16" t="s">
         <v>275</v>
       </c>
       <c r="G16">
-        <v>0.7</v>
+        <v>0.49</v>
       </c>
       <c r="H16" t="s">
         <v>17</v>
       </c>
       <c r="I16" t="s">
-        <v>68</v>
+        <v>178</v>
       </c>
       <c r="J16" t="s">
-        <v>68</v>
+        <v>178</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>319</v>
-      </c>
-      <c r="L16" t="s">
-        <v>320</v>
-      </c>
-      <c r="M16" t="s">
-        <v>321</v>
+        <v>503</v>
+      </c>
+      <c r="L16" s="3" t="s">
+        <v>504</v>
+      </c>
+      <c r="M16" s="3" t="s">
+        <v>505</v>
       </c>
     </row>
     <row r="17" spans="1:13" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>67</v>
+        <v>179</v>
       </c>
       <c r="B17" t="s">
-        <v>14</v>
+        <v>153</v>
       </c>
       <c r="C17" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D17" t="s">
         <v>44</v>
@@ -27492,144 +27600,144 @@
         <v>275</v>
       </c>
       <c r="G17">
-        <v>0.69</v>
+        <v>0.49</v>
       </c>
       <c r="H17" t="s">
         <v>17</v>
       </c>
       <c r="I17" t="s">
-        <v>68</v>
+        <v>180</v>
       </c>
       <c r="J17" t="s">
-        <v>68</v>
+        <v>180</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="L17" t="s">
-        <v>323</v>
-      </c>
-      <c r="M17" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+        <v>503</v>
+      </c>
+      <c r="L17" s="3" t="s">
+        <v>504</v>
+      </c>
+      <c r="M17" s="3" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>67</v>
+        <v>205</v>
       </c>
       <c r="B18" t="s">
-        <v>14</v>
+        <v>191</v>
       </c>
       <c r="C18" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="D18" t="s">
-        <v>30</v>
+        <v>51</v>
       </c>
       <c r="E18" t="s">
         <v>275</v>
       </c>
       <c r="G18">
-        <v>0.79</v>
+        <v>0.49</v>
       </c>
       <c r="H18" t="s">
         <v>17</v>
       </c>
       <c r="I18" t="s">
-        <v>68</v>
+        <v>527</v>
       </c>
       <c r="J18" t="s">
-        <v>68</v>
+        <v>527</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>325</v>
-      </c>
-      <c r="L18" t="s">
-        <v>324</v>
-      </c>
-      <c r="M18" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" ht="158.4" x14ac:dyDescent="0.3">
+        <v>528</v>
+      </c>
+      <c r="L18" s="3" t="s">
+        <v>529</v>
+      </c>
+      <c r="M18" s="3" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>69</v>
+        <v>239</v>
       </c>
       <c r="B19" t="s">
-        <v>14</v>
+        <v>218</v>
       </c>
       <c r="C19" t="s">
-        <v>73</v>
+        <v>33</v>
       </c>
       <c r="D19" t="s">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="E19" t="s">
         <v>275</v>
       </c>
       <c r="G19">
-        <v>0.95</v>
+        <v>0.5</v>
       </c>
       <c r="H19" t="s">
         <v>17</v>
       </c>
       <c r="I19" t="s">
-        <v>327</v>
+        <v>558</v>
       </c>
       <c r="J19" t="s">
-        <v>327</v>
+        <v>558</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>328</v>
-      </c>
-      <c r="L19" t="s">
-        <v>329</v>
-      </c>
-      <c r="M19" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" ht="158.4" x14ac:dyDescent="0.3">
+        <v>559</v>
+      </c>
+      <c r="L19" s="3" t="s">
+        <v>560</v>
+      </c>
+      <c r="M19" s="3" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="B20" t="s">
         <v>14</v>
       </c>
       <c r="C20" t="s">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="D20" t="s">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="E20" t="s">
         <v>275</v>
       </c>
       <c r="G20">
-        <v>0.95</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="H20" t="s">
         <v>17</v>
       </c>
       <c r="I20" t="s">
-        <v>327</v>
+        <v>308</v>
       </c>
       <c r="J20" t="s">
-        <v>327</v>
+        <v>308</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>331</v>
-      </c>
-      <c r="L20" t="s">
-        <v>330</v>
-      </c>
-      <c r="M20" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" ht="158.4" x14ac:dyDescent="0.3">
+        <v>309</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="M20" s="3" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>69</v>
+        <v>297</v>
       </c>
       <c r="B21" t="s">
         <v>14</v>
@@ -27644,223 +27752,223 @@
         <v>275</v>
       </c>
       <c r="G21">
-        <v>0.31</v>
+        <v>0.6</v>
       </c>
       <c r="H21" t="s">
         <v>17</v>
       </c>
       <c r="I21" t="s">
-        <v>332</v>
+        <v>298</v>
       </c>
       <c r="J21" t="s">
-        <v>332</v>
+        <v>298</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="L21" t="s">
-        <v>334</v>
-      </c>
-      <c r="M21" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" ht="158.4" x14ac:dyDescent="0.3">
+        <v>299</v>
+      </c>
+      <c r="L21" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="M21" s="3" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>69</v>
+        <v>302</v>
       </c>
       <c r="B22" t="s">
         <v>14</v>
       </c>
       <c r="C22" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D22" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E22" t="s">
         <v>275</v>
       </c>
       <c r="G22">
-        <v>0.43</v>
+        <v>0.6</v>
       </c>
       <c r="H22" t="s">
         <v>17</v>
       </c>
       <c r="I22" t="s">
-        <v>336</v>
+        <v>303</v>
       </c>
       <c r="J22" t="s">
-        <v>336</v>
+        <v>303</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="L22" t="s">
-        <v>338</v>
-      </c>
-      <c r="M22" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+        <v>299</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="M22" s="3" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>75</v>
+        <v>304</v>
       </c>
       <c r="B23" t="s">
         <v>14</v>
       </c>
       <c r="C23" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="D23" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="E23" t="s">
         <v>275</v>
       </c>
       <c r="G23">
-        <v>0.99</v>
+        <v>0.6</v>
       </c>
       <c r="H23" t="s">
         <v>17</v>
       </c>
       <c r="I23" t="s">
-        <v>76</v>
+        <v>305</v>
       </c>
       <c r="J23" t="s">
-        <v>76</v>
+        <v>305</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>340</v>
-      </c>
-      <c r="L23" t="s">
-        <v>341</v>
-      </c>
-      <c r="M23" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" ht="409.6" x14ac:dyDescent="0.3">
+        <v>299</v>
+      </c>
+      <c r="L23" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="M23" s="3" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>343</v>
+        <v>306</v>
       </c>
       <c r="B24" t="s">
         <v>14</v>
       </c>
       <c r="C24" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="D24" t="s">
-        <v>344</v>
+        <v>33</v>
       </c>
       <c r="E24" t="s">
         <v>275</v>
       </c>
       <c r="G24">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="H24" t="s">
         <v>17</v>
       </c>
       <c r="I24" t="s">
-        <v>345</v>
+        <v>307</v>
       </c>
       <c r="J24" t="s">
-        <v>345</v>
+        <v>307</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>346</v>
-      </c>
-      <c r="L24" t="s">
-        <v>347</v>
-      </c>
-      <c r="M24" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" ht="100.8" x14ac:dyDescent="0.3">
+        <v>299</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="M24" s="3" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" ht="72" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>343</v>
+        <v>47</v>
       </c>
       <c r="B25" t="s">
         <v>14</v>
       </c>
       <c r="C25" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="D25" t="s">
-        <v>20</v>
+        <v>96</v>
       </c>
       <c r="E25" t="s">
         <v>275</v>
       </c>
       <c r="G25">
-        <v>0.99</v>
+        <v>0.62</v>
       </c>
       <c r="H25" t="s">
         <v>17</v>
       </c>
       <c r="I25" t="s">
-        <v>345</v>
+        <v>293</v>
       </c>
       <c r="J25" t="s">
-        <v>345</v>
+        <v>293</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>349</v>
-      </c>
-      <c r="L25" t="s">
-        <v>350</v>
-      </c>
-      <c r="M25" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" ht="187.2" x14ac:dyDescent="0.3">
+        <v>294</v>
+      </c>
+      <c r="L25" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="M25" s="3" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" ht="302.39999999999998" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>343</v>
+        <v>47</v>
       </c>
       <c r="B26" t="s">
         <v>14</v>
       </c>
       <c r="C26" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D26" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="E26" t="s">
         <v>275</v>
       </c>
       <c r="G26">
-        <v>0.85</v>
+        <v>0.63</v>
       </c>
       <c r="H26" t="s">
         <v>17</v>
       </c>
       <c r="I26" t="s">
-        <v>345</v>
+        <v>49</v>
       </c>
       <c r="J26" t="s">
-        <v>345</v>
+        <v>49</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>352</v>
-      </c>
-      <c r="L26" t="s">
-        <v>351</v>
-      </c>
-      <c r="M26" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13" ht="129.6" x14ac:dyDescent="0.3">
+        <v>290</v>
+      </c>
+      <c r="L26" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="M26" s="3" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" ht="230.4" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>354</v>
+        <v>128</v>
       </c>
       <c r="B27" t="s">
-        <v>14</v>
+        <v>117</v>
       </c>
       <c r="C27" t="s">
         <v>35</v>
@@ -27872,945 +27980,945 @@
         <v>275</v>
       </c>
       <c r="G27">
-        <v>0.79</v>
+        <v>0.63</v>
       </c>
       <c r="H27" t="s">
         <v>17</v>
       </c>
       <c r="I27" t="s">
-        <v>355</v>
+        <v>459</v>
       </c>
       <c r="J27" t="s">
-        <v>355</v>
+        <v>459</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>356</v>
-      </c>
-      <c r="L27" t="s">
-        <v>357</v>
-      </c>
-      <c r="M27" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" ht="129.6" x14ac:dyDescent="0.3">
+        <v>463</v>
+      </c>
+      <c r="L27" s="3" t="s">
+        <v>462</v>
+      </c>
+      <c r="M27" s="3" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>79</v>
+        <v>481</v>
       </c>
       <c r="B28" t="s">
-        <v>14</v>
+        <v>135</v>
       </c>
       <c r="C28" t="s">
-        <v>73</v>
+        <v>447</v>
       </c>
       <c r="D28" t="s">
-        <v>15</v>
+        <v>448</v>
       </c>
       <c r="E28" t="s">
         <v>275</v>
       </c>
       <c r="G28">
-        <v>0.79</v>
+        <v>0.65</v>
       </c>
       <c r="H28" t="s">
         <v>17</v>
       </c>
       <c r="I28" t="s">
-        <v>359</v>
+        <v>482</v>
       </c>
       <c r="J28" t="s">
-        <v>359</v>
+        <v>482</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>360</v>
-      </c>
-      <c r="L28" t="s">
-        <v>361</v>
-      </c>
-      <c r="M28" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" ht="129.6" x14ac:dyDescent="0.3">
+        <v>483</v>
+      </c>
+      <c r="L28" s="3" t="s">
+        <v>484</v>
+      </c>
+      <c r="M28" s="3" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>79</v>
+        <v>486</v>
       </c>
       <c r="B29" t="s">
-        <v>14</v>
+        <v>135</v>
       </c>
       <c r="C29" t="s">
-        <v>15</v>
+        <v>447</v>
       </c>
       <c r="D29" t="s">
-        <v>16</v>
+        <v>448</v>
       </c>
       <c r="E29" t="s">
         <v>275</v>
       </c>
       <c r="G29">
-        <v>0.75</v>
+        <v>0.65</v>
       </c>
       <c r="H29" t="s">
         <v>17</v>
       </c>
       <c r="I29" t="s">
-        <v>359</v>
+        <v>487</v>
       </c>
       <c r="J29" t="s">
-        <v>359</v>
+        <v>487</v>
       </c>
       <c r="K29" s="3" t="s">
-        <v>363</v>
-      </c>
-      <c r="L29" t="s">
-        <v>362</v>
-      </c>
-      <c r="M29" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13" ht="86.4" x14ac:dyDescent="0.3">
+        <v>483</v>
+      </c>
+      <c r="L29" s="3" t="s">
+        <v>484</v>
+      </c>
+      <c r="M29" s="3" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>79</v>
+        <v>488</v>
       </c>
       <c r="B30" t="s">
-        <v>14</v>
+        <v>135</v>
       </c>
       <c r="C30" t="s">
-        <v>27</v>
+        <v>447</v>
       </c>
       <c r="D30" t="s">
-        <v>28</v>
+        <v>448</v>
       </c>
       <c r="E30" t="s">
         <v>275</v>
       </c>
       <c r="G30">
-        <v>0.97</v>
+        <v>0.65</v>
       </c>
       <c r="H30" t="s">
         <v>17</v>
       </c>
       <c r="I30" t="s">
-        <v>365</v>
+        <v>489</v>
       </c>
       <c r="J30" t="s">
-        <v>365</v>
+        <v>489</v>
       </c>
       <c r="K30" s="3" t="s">
-        <v>366</v>
-      </c>
-      <c r="L30" t="s">
-        <v>367</v>
-      </c>
-      <c r="M30" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13" ht="158.4" x14ac:dyDescent="0.3">
+        <v>483</v>
+      </c>
+      <c r="L30" s="3" t="s">
+        <v>484</v>
+      </c>
+      <c r="M30" s="3" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>79</v>
+        <v>490</v>
       </c>
       <c r="B31" t="s">
-        <v>14</v>
+        <v>135</v>
       </c>
       <c r="C31" t="s">
-        <v>35</v>
+        <v>447</v>
       </c>
       <c r="D31" t="s">
-        <v>36</v>
+        <v>448</v>
       </c>
       <c r="E31" t="s">
         <v>275</v>
       </c>
       <c r="G31">
-        <v>0.31</v>
+        <v>0.65</v>
       </c>
       <c r="H31" t="s">
         <v>17</v>
       </c>
       <c r="I31" t="s">
-        <v>369</v>
+        <v>491</v>
       </c>
       <c r="J31" t="s">
-        <v>369</v>
+        <v>491</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>370</v>
-      </c>
-      <c r="L31" t="s">
-        <v>371</v>
-      </c>
-      <c r="M31" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13" ht="302.39999999999998" x14ac:dyDescent="0.3">
+        <v>483</v>
+      </c>
+      <c r="L31" s="3" t="s">
+        <v>484</v>
+      </c>
+      <c r="M31" s="3" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>81</v>
+        <v>492</v>
       </c>
       <c r="B32" t="s">
-        <v>14</v>
+        <v>135</v>
       </c>
       <c r="C32" t="s">
-        <v>23</v>
+        <v>447</v>
       </c>
       <c r="D32" t="s">
-        <v>24</v>
+        <v>448</v>
       </c>
       <c r="E32" t="s">
         <v>275</v>
       </c>
       <c r="G32">
-        <v>0.81</v>
+        <v>0.65</v>
       </c>
       <c r="H32" t="s">
         <v>17</v>
       </c>
       <c r="I32" t="s">
-        <v>83</v>
+        <v>493</v>
       </c>
       <c r="J32" t="s">
-        <v>83</v>
+        <v>493</v>
       </c>
       <c r="K32" s="3" t="s">
-        <v>373</v>
-      </c>
-      <c r="L32" t="s">
-        <v>374</v>
-      </c>
-      <c r="M32" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+        <v>483</v>
+      </c>
+      <c r="L32" s="3" t="s">
+        <v>484</v>
+      </c>
+      <c r="M32" s="3" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>376</v>
+        <v>494</v>
       </c>
       <c r="B33" t="s">
-        <v>14</v>
+        <v>135</v>
       </c>
       <c r="C33" t="s">
-        <v>23</v>
+        <v>447</v>
       </c>
       <c r="D33" t="s">
-        <v>24</v>
+        <v>448</v>
       </c>
       <c r="E33" t="s">
         <v>275</v>
       </c>
       <c r="G33">
-        <v>0.98</v>
+        <v>0.65</v>
       </c>
       <c r="H33" t="s">
         <v>17</v>
       </c>
       <c r="I33" t="s">
-        <v>377</v>
+        <v>495</v>
       </c>
       <c r="J33" t="s">
-        <v>377</v>
+        <v>495</v>
       </c>
       <c r="K33" s="3" t="s">
-        <v>378</v>
-      </c>
-      <c r="L33" t="s">
-        <v>374</v>
-      </c>
-      <c r="M33" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+        <v>483</v>
+      </c>
+      <c r="L33" s="3" t="s">
+        <v>484</v>
+      </c>
+      <c r="M33" s="3" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>376</v>
+        <v>496</v>
       </c>
       <c r="B34" t="s">
-        <v>14</v>
+        <v>135</v>
       </c>
       <c r="C34" t="s">
-        <v>24</v>
+        <v>447</v>
       </c>
       <c r="D34" t="s">
-        <v>42</v>
+        <v>448</v>
       </c>
       <c r="E34" t="s">
         <v>275</v>
       </c>
       <c r="G34">
-        <v>0.98</v>
+        <v>0.65</v>
       </c>
       <c r="H34" t="s">
         <v>17</v>
       </c>
       <c r="I34" t="s">
-        <v>377</v>
+        <v>497</v>
       </c>
       <c r="J34" t="s">
-        <v>377</v>
+        <v>497</v>
       </c>
       <c r="K34" s="3" t="s">
-        <v>380</v>
-      </c>
-      <c r="L34" t="s">
-        <v>379</v>
-      </c>
-      <c r="M34" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13" ht="216" x14ac:dyDescent="0.3">
+        <v>483</v>
+      </c>
+      <c r="L34" s="3" t="s">
+        <v>484</v>
+      </c>
+      <c r="M34" s="3" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>381</v>
+        <v>67</v>
       </c>
       <c r="B35" t="s">
         <v>14</v>
       </c>
       <c r="C35" t="s">
-        <v>73</v>
+        <v>29</v>
       </c>
       <c r="D35" t="s">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="E35" t="s">
         <v>275</v>
       </c>
       <c r="G35">
-        <v>0.96</v>
+        <v>0.69</v>
       </c>
       <c r="H35" t="s">
         <v>17</v>
       </c>
       <c r="I35" t="s">
-        <v>382</v>
+        <v>68</v>
       </c>
       <c r="J35" t="s">
-        <v>382</v>
+        <v>68</v>
       </c>
       <c r="K35" s="3" t="s">
-        <v>383</v>
-      </c>
-      <c r="L35" t="s">
-        <v>384</v>
-      </c>
-      <c r="M35" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+        <v>322</v>
+      </c>
+      <c r="L35" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="M35" s="3" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" ht="273.60000000000002" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>381</v>
+        <v>67</v>
       </c>
       <c r="B36" t="s">
         <v>14</v>
       </c>
       <c r="C36" t="s">
-        <v>15</v>
+        <v>318</v>
       </c>
       <c r="D36" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="E36" t="s">
         <v>275</v>
       </c>
       <c r="G36">
-        <v>0.99</v>
+        <v>0.7</v>
       </c>
       <c r="H36" t="s">
         <v>17</v>
       </c>
       <c r="I36" t="s">
-        <v>382</v>
+        <v>68</v>
       </c>
       <c r="J36" t="s">
-        <v>382</v>
+        <v>68</v>
       </c>
       <c r="K36" s="3" t="s">
-        <v>386</v>
-      </c>
-      <c r="L36" t="s">
-        <v>385</v>
-      </c>
-      <c r="M36" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13" ht="216" x14ac:dyDescent="0.3">
+        <v>319</v>
+      </c>
+      <c r="L36" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="M36" s="3" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>388</v>
+        <v>138</v>
       </c>
       <c r="B37" t="s">
-        <v>14</v>
+        <v>135</v>
       </c>
       <c r="C37" t="s">
-        <v>73</v>
+        <v>30</v>
       </c>
       <c r="D37" t="s">
-        <v>15</v>
+        <v>51</v>
       </c>
       <c r="E37" t="s">
         <v>275</v>
       </c>
       <c r="G37">
-        <v>0.96</v>
+        <v>0.71</v>
       </c>
       <c r="H37" t="s">
         <v>17</v>
       </c>
       <c r="I37" t="s">
-        <v>389</v>
+        <v>473</v>
       </c>
       <c r="J37" t="s">
-        <v>389</v>
+        <v>473</v>
       </c>
       <c r="K37" s="3" t="s">
-        <v>390</v>
-      </c>
-      <c r="L37" t="s">
-        <v>391</v>
-      </c>
-      <c r="M37" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="38" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+        <v>474</v>
+      </c>
+      <c r="L37" s="3" t="s">
+        <v>475</v>
+      </c>
+      <c r="M37" s="3" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>388</v>
+        <v>152</v>
       </c>
       <c r="B38" t="s">
-        <v>14</v>
+        <v>153</v>
       </c>
       <c r="C38" t="s">
-        <v>15</v>
+        <v>447</v>
       </c>
       <c r="D38" t="s">
-        <v>16</v>
+        <v>448</v>
       </c>
       <c r="E38" t="s">
         <v>275</v>
       </c>
       <c r="G38">
-        <v>0.99</v>
+        <v>0.73</v>
       </c>
       <c r="H38" t="s">
         <v>17</v>
       </c>
       <c r="I38" t="s">
-        <v>389</v>
+        <v>487</v>
       </c>
       <c r="J38" t="s">
-        <v>389</v>
+        <v>487</v>
       </c>
       <c r="K38" s="3" t="s">
-        <v>386</v>
-      </c>
-      <c r="L38" t="s">
-        <v>392</v>
-      </c>
-      <c r="M38" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="39" spans="1:13" ht="100.8" x14ac:dyDescent="0.3">
+        <v>506</v>
+      </c>
+      <c r="L38" s="3" t="s">
+        <v>507</v>
+      </c>
+      <c r="M38" s="3" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>394</v>
+        <v>509</v>
       </c>
       <c r="B39" t="s">
-        <v>14</v>
+        <v>153</v>
       </c>
       <c r="C39" t="s">
-        <v>73</v>
+        <v>447</v>
       </c>
       <c r="D39" t="s">
-        <v>15</v>
+        <v>448</v>
       </c>
       <c r="E39" t="s">
         <v>275</v>
       </c>
       <c r="G39">
-        <v>0.99</v>
+        <v>0.73</v>
       </c>
       <c r="H39" t="s">
         <v>17</v>
       </c>
       <c r="I39" t="s">
-        <v>395</v>
+        <v>495</v>
       </c>
       <c r="J39" t="s">
-        <v>395</v>
+        <v>495</v>
       </c>
       <c r="K39" s="3" t="s">
-        <v>396</v>
-      </c>
-      <c r="L39" t="s">
-        <v>397</v>
-      </c>
-      <c r="M39" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="40" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+        <v>506</v>
+      </c>
+      <c r="L39" s="3" t="s">
+        <v>507</v>
+      </c>
+      <c r="M39" s="3" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>394</v>
+        <v>510</v>
       </c>
       <c r="B40" t="s">
-        <v>14</v>
+        <v>153</v>
       </c>
       <c r="C40" t="s">
-        <v>15</v>
+        <v>447</v>
       </c>
       <c r="D40" t="s">
-        <v>16</v>
+        <v>448</v>
       </c>
       <c r="E40" t="s">
         <v>275</v>
       </c>
       <c r="G40">
-        <v>0.99</v>
+        <v>0.73</v>
       </c>
       <c r="H40" t="s">
         <v>17</v>
       </c>
       <c r="I40" t="s">
-        <v>395</v>
+        <v>493</v>
       </c>
       <c r="J40" t="s">
-        <v>395</v>
+        <v>493</v>
       </c>
       <c r="K40" s="3" t="s">
-        <v>399</v>
-      </c>
-      <c r="L40" t="s">
-        <v>398</v>
-      </c>
-      <c r="M40" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="41" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+        <v>506</v>
+      </c>
+      <c r="L40" s="3" t="s">
+        <v>507</v>
+      </c>
+      <c r="M40" s="3" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>93</v>
+        <v>511</v>
       </c>
       <c r="B41" t="s">
-        <v>94</v>
+        <v>153</v>
       </c>
       <c r="C41" t="s">
-        <v>27</v>
+        <v>447</v>
       </c>
       <c r="D41" t="s">
-        <v>28</v>
+        <v>448</v>
       </c>
       <c r="E41" t="s">
         <v>275</v>
       </c>
       <c r="G41">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="H41" t="s">
         <v>17</v>
       </c>
       <c r="I41" t="s">
-        <v>95</v>
+        <v>491</v>
       </c>
       <c r="J41" t="s">
-        <v>95</v>
+        <v>491</v>
       </c>
       <c r="K41" s="3" t="s">
-        <v>401</v>
-      </c>
-      <c r="L41" t="s">
-        <v>402</v>
-      </c>
-      <c r="M41" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="42" spans="1:13" ht="158.4" x14ac:dyDescent="0.3">
+        <v>506</v>
+      </c>
+      <c r="L41" s="3" t="s">
+        <v>507</v>
+      </c>
+      <c r="M41" s="3" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>98</v>
+        <v>512</v>
       </c>
       <c r="B42" t="s">
-        <v>94</v>
+        <v>153</v>
       </c>
       <c r="C42" t="s">
-        <v>35</v>
+        <v>447</v>
       </c>
       <c r="D42" t="s">
-        <v>36</v>
+        <v>448</v>
       </c>
       <c r="E42" t="s">
         <v>275</v>
       </c>
       <c r="G42">
-        <v>0.41</v>
+        <v>0.73</v>
       </c>
       <c r="H42" t="s">
         <v>17</v>
       </c>
       <c r="I42" t="s">
-        <v>404</v>
+        <v>489</v>
       </c>
       <c r="J42" t="s">
-        <v>404</v>
+        <v>489</v>
       </c>
       <c r="K42" s="3" t="s">
-        <v>405</v>
-      </c>
-      <c r="L42" t="s">
-        <v>406</v>
-      </c>
-      <c r="M42" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="43" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+        <v>506</v>
+      </c>
+      <c r="L42" s="3" t="s">
+        <v>507</v>
+      </c>
+      <c r="M42" s="3" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>100</v>
+        <v>513</v>
       </c>
       <c r="B43" t="s">
-        <v>94</v>
+        <v>153</v>
       </c>
       <c r="C43" t="s">
-        <v>73</v>
+        <v>447</v>
       </c>
       <c r="D43" t="s">
-        <v>15</v>
+        <v>448</v>
       </c>
       <c r="E43" t="s">
         <v>275</v>
       </c>
       <c r="G43">
-        <v>0.99</v>
+        <v>0.73</v>
       </c>
       <c r="H43" t="s">
         <v>17</v>
       </c>
       <c r="I43" t="s">
-        <v>408</v>
+        <v>497</v>
       </c>
       <c r="J43" t="s">
-        <v>408</v>
+        <v>497</v>
       </c>
       <c r="K43" s="3" t="s">
-        <v>409</v>
-      </c>
-      <c r="L43" t="s">
-        <v>410</v>
-      </c>
-      <c r="M43" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="44" spans="1:13" ht="129.6" x14ac:dyDescent="0.3">
+        <v>506</v>
+      </c>
+      <c r="L43" s="3" t="s">
+        <v>507</v>
+      </c>
+      <c r="M43" s="3" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>412</v>
+        <v>516</v>
       </c>
       <c r="B44" t="s">
-        <v>94</v>
+        <v>153</v>
       </c>
       <c r="C44" t="s">
-        <v>73</v>
+        <v>447</v>
       </c>
       <c r="D44" t="s">
-        <v>15</v>
+        <v>448</v>
       </c>
       <c r="E44" t="s">
         <v>275</v>
       </c>
       <c r="G44">
-        <v>0.84</v>
+        <v>0.73</v>
       </c>
       <c r="H44" t="s">
         <v>17</v>
       </c>
       <c r="I44" t="s">
-        <v>413</v>
+        <v>517</v>
       </c>
       <c r="J44" t="s">
-        <v>413</v>
+        <v>517</v>
       </c>
       <c r="K44" s="3" t="s">
-        <v>414</v>
-      </c>
-      <c r="L44" t="s">
-        <v>415</v>
-      </c>
-      <c r="M44" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="45" spans="1:13" ht="129.6" x14ac:dyDescent="0.3">
+        <v>506</v>
+      </c>
+      <c r="L44" s="3" t="s">
+        <v>507</v>
+      </c>
+      <c r="M44" s="3" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>417</v>
+        <v>518</v>
       </c>
       <c r="B45" t="s">
-        <v>94</v>
+        <v>153</v>
       </c>
       <c r="C45" t="s">
-        <v>73</v>
+        <v>447</v>
       </c>
       <c r="D45" t="s">
-        <v>15</v>
+        <v>448</v>
       </c>
       <c r="E45" t="s">
         <v>275</v>
       </c>
       <c r="G45">
-        <v>0.9</v>
+        <v>0.73</v>
       </c>
       <c r="H45" t="s">
         <v>17</v>
       </c>
       <c r="I45" t="s">
-        <v>418</v>
+        <v>519</v>
       </c>
       <c r="J45" t="s">
-        <v>418</v>
+        <v>519</v>
       </c>
       <c r="K45" s="3" t="s">
-        <v>419</v>
-      </c>
-      <c r="L45" t="s">
-        <v>420</v>
-      </c>
-      <c r="M45" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="46" spans="1:13" ht="129.6" x14ac:dyDescent="0.3">
+        <v>506</v>
+      </c>
+      <c r="L45" s="3" t="s">
+        <v>507</v>
+      </c>
+      <c r="M45" s="3" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>422</v>
+        <v>520</v>
       </c>
       <c r="B46" t="s">
-        <v>94</v>
+        <v>153</v>
       </c>
       <c r="C46" t="s">
-        <v>73</v>
+        <v>447</v>
       </c>
       <c r="D46" t="s">
-        <v>15</v>
+        <v>448</v>
       </c>
       <c r="E46" t="s">
         <v>275</v>
       </c>
       <c r="G46">
-        <v>0.92</v>
+        <v>0.73</v>
       </c>
       <c r="H46" t="s">
         <v>17</v>
       </c>
       <c r="I46" t="s">
-        <v>423</v>
+        <v>521</v>
       </c>
       <c r="J46" t="s">
-        <v>423</v>
+        <v>521</v>
       </c>
       <c r="K46" s="3" t="s">
-        <v>424</v>
-      </c>
-      <c r="L46" t="s">
-        <v>425</v>
-      </c>
-      <c r="M46" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="47" spans="1:13" ht="129.6" x14ac:dyDescent="0.3">
+        <v>506</v>
+      </c>
+      <c r="L46" s="3" t="s">
+        <v>507</v>
+      </c>
+      <c r="M46" s="3" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" ht="388.8" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>427</v>
+        <v>40</v>
       </c>
       <c r="B47" t="s">
-        <v>94</v>
+        <v>14</v>
       </c>
       <c r="C47" t="s">
-        <v>73</v>
+        <v>45</v>
       </c>
       <c r="D47" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="E47" t="s">
         <v>275</v>
       </c>
       <c r="G47">
-        <v>0.84</v>
+        <v>0.74</v>
       </c>
       <c r="H47" t="s">
         <v>17</v>
       </c>
       <c r="I47" t="s">
-        <v>428</v>
+        <v>46</v>
       </c>
       <c r="J47" t="s">
-        <v>428</v>
+        <v>46</v>
       </c>
       <c r="K47" s="3" t="s">
-        <v>414</v>
-      </c>
-      <c r="L47" t="s">
-        <v>429</v>
-      </c>
-      <c r="M47" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="48" spans="1:13" ht="129.6" x14ac:dyDescent="0.3">
+        <v>281</v>
+      </c>
+      <c r="L47" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="M47" s="3" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" ht="273.60000000000002" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>431</v>
+        <v>141</v>
       </c>
       <c r="B48" t="s">
-        <v>94</v>
+        <v>135</v>
       </c>
       <c r="C48" t="s">
-        <v>73</v>
+        <v>447</v>
       </c>
       <c r="D48" t="s">
-        <v>15</v>
+        <v>448</v>
       </c>
       <c r="E48" t="s">
         <v>275</v>
       </c>
       <c r="G48">
-        <v>0.9</v>
+        <v>0.74</v>
       </c>
       <c r="H48" t="s">
         <v>17</v>
       </c>
       <c r="I48" t="s">
-        <v>432</v>
+        <v>477</v>
       </c>
       <c r="J48" t="s">
-        <v>432</v>
+        <v>477</v>
       </c>
       <c r="K48" s="3" t="s">
-        <v>419</v>
-      </c>
-      <c r="L48" t="s">
-        <v>420</v>
-      </c>
-      <c r="M48" t="s">
-        <v>421</v>
+        <v>478</v>
+      </c>
+      <c r="L48" s="3" t="s">
+        <v>479</v>
+      </c>
+      <c r="M48" s="3" t="s">
+        <v>480</v>
       </c>
     </row>
     <row r="49" spans="1:13" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>433</v>
+        <v>79</v>
       </c>
       <c r="B49" t="s">
-        <v>94</v>
+        <v>14</v>
       </c>
       <c r="C49" t="s">
-        <v>73</v>
+        <v>15</v>
       </c>
       <c r="D49" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E49" t="s">
         <v>275</v>
       </c>
       <c r="G49">
-        <v>0.91</v>
+        <v>0.75</v>
       </c>
       <c r="H49" t="s">
         <v>17</v>
       </c>
       <c r="I49" t="s">
-        <v>434</v>
+        <v>359</v>
       </c>
       <c r="J49" t="s">
-        <v>434</v>
+        <v>359</v>
       </c>
       <c r="K49" s="3" t="s">
-        <v>424</v>
-      </c>
-      <c r="L49" t="s">
-        <v>435</v>
-      </c>
-      <c r="M49" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="50" spans="1:13" ht="129.6" x14ac:dyDescent="0.3">
+        <v>363</v>
+      </c>
+      <c r="L49" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="M49" s="3" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" ht="72" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>437</v>
+        <v>67</v>
       </c>
       <c r="B50" t="s">
-        <v>94</v>
+        <v>14</v>
       </c>
       <c r="C50" t="s">
-        <v>73</v>
+        <v>45</v>
       </c>
       <c r="D50" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="E50" t="s">
         <v>275</v>
       </c>
       <c r="G50">
-        <v>0.84</v>
+        <v>0.79</v>
       </c>
       <c r="H50" t="s">
         <v>17</v>
       </c>
       <c r="I50" t="s">
-        <v>438</v>
+        <v>68</v>
       </c>
       <c r="J50" t="s">
-        <v>438</v>
+        <v>68</v>
       </c>
       <c r="K50" s="3" t="s">
-        <v>414</v>
-      </c>
-      <c r="L50" t="s">
-        <v>429</v>
-      </c>
-      <c r="M50" t="s">
-        <v>430</v>
+        <v>325</v>
+      </c>
+      <c r="L50" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="M50" s="3" t="s">
+        <v>326</v>
       </c>
     </row>
     <row r="51" spans="1:13" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>439</v>
+        <v>354</v>
       </c>
       <c r="B51" t="s">
-        <v>94</v>
+        <v>14</v>
       </c>
       <c r="C51" t="s">
-        <v>73</v>
+        <v>35</v>
       </c>
       <c r="D51" t="s">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="E51" t="s">
         <v>275</v>
       </c>
       <c r="G51">
-        <v>0.9</v>
+        <v>0.79</v>
       </c>
       <c r="H51" t="s">
         <v>17</v>
       </c>
       <c r="I51" t="s">
-        <v>440</v>
+        <v>355</v>
       </c>
       <c r="J51" t="s">
-        <v>440</v>
+        <v>355</v>
       </c>
       <c r="K51" s="3" t="s">
-        <v>419</v>
-      </c>
-      <c r="L51" t="s">
-        <v>420</v>
-      </c>
-      <c r="M51" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="52" spans="1:13" ht="129.6" x14ac:dyDescent="0.3">
+        <v>356</v>
+      </c>
+      <c r="L51" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="M51" s="3" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" ht="144" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>441</v>
+        <v>79</v>
       </c>
       <c r="B52" t="s">
-        <v>94</v>
+        <v>14</v>
       </c>
       <c r="C52" t="s">
         <v>73</v>
@@ -28822,299 +28930,299 @@
         <v>275</v>
       </c>
       <c r="G52">
-        <v>0.92</v>
+        <v>0.79</v>
       </c>
       <c r="H52" t="s">
         <v>17</v>
       </c>
       <c r="I52" t="s">
-        <v>442</v>
+        <v>359</v>
       </c>
       <c r="J52" t="s">
-        <v>442</v>
+        <v>359</v>
       </c>
       <c r="K52" s="3" t="s">
-        <v>424</v>
-      </c>
-      <c r="L52" t="s">
-        <v>425</v>
-      </c>
-      <c r="M52" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="53" spans="1:13" ht="129.6" x14ac:dyDescent="0.3">
+        <v>360</v>
+      </c>
+      <c r="L52" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="M52" s="3" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>116</v>
+        <v>157</v>
       </c>
       <c r="B53" t="s">
-        <v>117</v>
+        <v>153</v>
       </c>
       <c r="C53" t="s">
-        <v>73</v>
+        <v>45</v>
       </c>
       <c r="D53" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="E53" t="s">
         <v>275</v>
       </c>
       <c r="G53">
-        <v>0.9</v>
+        <v>0.79</v>
       </c>
       <c r="H53" t="s">
         <v>17</v>
       </c>
       <c r="I53" t="s">
-        <v>443</v>
+        <v>158</v>
       </c>
       <c r="J53" t="s">
-        <v>443</v>
+        <v>158</v>
       </c>
       <c r="K53" s="3" t="s">
-        <v>444</v>
-      </c>
-      <c r="L53" t="s">
-        <v>445</v>
-      </c>
-      <c r="M53" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="54" spans="1:13" ht="244.8" x14ac:dyDescent="0.3">
+        <v>514</v>
+      </c>
+      <c r="L53" s="3" t="s">
+        <v>505</v>
+      </c>
+      <c r="M53" s="3" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>116</v>
+        <v>171</v>
       </c>
       <c r="B54" t="s">
-        <v>117</v>
+        <v>153</v>
       </c>
       <c r="C54" t="s">
-        <v>447</v>
+        <v>45</v>
       </c>
       <c r="D54" t="s">
-        <v>448</v>
+        <v>30</v>
       </c>
       <c r="E54" t="s">
         <v>275</v>
       </c>
       <c r="G54">
-        <v>0.86</v>
+        <v>0.79</v>
       </c>
       <c r="H54" t="s">
         <v>17</v>
       </c>
       <c r="I54" t="s">
-        <v>449</v>
+        <v>172</v>
       </c>
       <c r="J54" t="s">
-        <v>449</v>
+        <v>172</v>
       </c>
       <c r="K54" s="3" t="s">
-        <v>450</v>
-      </c>
-      <c r="L54" t="s">
-        <v>451</v>
-      </c>
-      <c r="M54" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="55" spans="1:13" ht="244.8" x14ac:dyDescent="0.3">
+        <v>514</v>
+      </c>
+      <c r="L54" s="3" t="s">
+        <v>505</v>
+      </c>
+      <c r="M54" s="3" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>119</v>
+        <v>179</v>
       </c>
       <c r="B55" t="s">
-        <v>117</v>
+        <v>153</v>
       </c>
       <c r="C55" t="s">
-        <v>447</v>
+        <v>45</v>
       </c>
       <c r="D55" t="s">
-        <v>448</v>
+        <v>30</v>
       </c>
       <c r="E55" t="s">
         <v>275</v>
       </c>
       <c r="G55">
-        <v>0.86</v>
+        <v>0.79</v>
       </c>
       <c r="H55" t="s">
         <v>17</v>
       </c>
       <c r="I55" t="s">
-        <v>453</v>
+        <v>180</v>
       </c>
       <c r="J55" t="s">
-        <v>453</v>
+        <v>180</v>
       </c>
       <c r="K55" s="3" t="s">
-        <v>450</v>
-      </c>
-      <c r="L55" t="s">
-        <v>451</v>
-      </c>
-      <c r="M55" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="56" spans="1:13" ht="129.6" x14ac:dyDescent="0.3">
+        <v>514</v>
+      </c>
+      <c r="L55" s="3" t="s">
+        <v>505</v>
+      </c>
+      <c r="M55" s="3" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" ht="72" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>128</v>
+        <v>93</v>
       </c>
       <c r="B56" t="s">
-        <v>117</v>
+        <v>94</v>
       </c>
       <c r="C56" t="s">
-        <v>73</v>
+        <v>27</v>
       </c>
       <c r="D56" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="E56" t="s">
         <v>275</v>
       </c>
       <c r="G56">
-        <v>0.94</v>
+        <v>0.8</v>
       </c>
       <c r="H56" t="s">
         <v>17</v>
       </c>
       <c r="I56" t="s">
-        <v>454</v>
+        <v>95</v>
       </c>
       <c r="J56" t="s">
-        <v>454</v>
+        <v>95</v>
       </c>
       <c r="K56" s="3" t="s">
-        <v>455</v>
-      </c>
-      <c r="L56" t="s">
-        <v>456</v>
-      </c>
-      <c r="M56" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="57" spans="1:13" ht="129.6" x14ac:dyDescent="0.3">
+        <v>401</v>
+      </c>
+      <c r="L56" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="M56" s="3" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" ht="302.39999999999998" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>128</v>
+        <v>81</v>
       </c>
       <c r="B57" t="s">
-        <v>117</v>
+        <v>14</v>
       </c>
       <c r="C57" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="D57" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E57" t="s">
         <v>275</v>
       </c>
       <c r="G57">
-        <v>0.94</v>
+        <v>0.81</v>
       </c>
       <c r="H57" t="s">
         <v>17</v>
       </c>
       <c r="I57" t="s">
-        <v>454</v>
+        <v>83</v>
       </c>
       <c r="J57" t="s">
-        <v>454</v>
+        <v>83</v>
       </c>
       <c r="K57" s="3" t="s">
-        <v>458</v>
-      </c>
-      <c r="L57" t="s">
-        <v>457</v>
-      </c>
-      <c r="M57" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="58" spans="1:13" ht="216" x14ac:dyDescent="0.3">
+        <v>373</v>
+      </c>
+      <c r="L57" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="M57" s="3" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" ht="302.39999999999998" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>128</v>
+        <v>562</v>
       </c>
       <c r="B58" t="s">
-        <v>117</v>
+        <v>218</v>
       </c>
       <c r="C58" t="s">
-        <v>33</v>
+        <v>447</v>
       </c>
       <c r="D58" t="s">
-        <v>35</v>
+        <v>448</v>
       </c>
       <c r="E58" t="s">
         <v>275</v>
       </c>
       <c r="G58">
-        <v>0.43</v>
+        <v>0.83</v>
       </c>
       <c r="H58" t="s">
         <v>17</v>
       </c>
       <c r="I58" t="s">
-        <v>459</v>
+        <v>563</v>
       </c>
       <c r="J58" t="s">
-        <v>459</v>
+        <v>563</v>
       </c>
       <c r="K58" s="3" t="s">
-        <v>460</v>
-      </c>
-      <c r="L58" t="s">
-        <v>461</v>
-      </c>
-      <c r="M58" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="59" spans="1:13" ht="201.6" x14ac:dyDescent="0.3">
+        <v>564</v>
+      </c>
+      <c r="L58" s="3" t="s">
+        <v>565</v>
+      </c>
+      <c r="M58" s="3" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>128</v>
+        <v>412</v>
       </c>
       <c r="B59" t="s">
-        <v>117</v>
+        <v>94</v>
       </c>
       <c r="C59" t="s">
-        <v>35</v>
+        <v>73</v>
       </c>
       <c r="D59" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="E59" t="s">
         <v>275</v>
       </c>
       <c r="G59">
-        <v>0.63</v>
+        <v>0.84</v>
       </c>
       <c r="H59" t="s">
         <v>17</v>
       </c>
       <c r="I59" t="s">
-        <v>459</v>
+        <v>413</v>
       </c>
       <c r="J59" t="s">
-        <v>459</v>
+        <v>413</v>
       </c>
       <c r="K59" s="3" t="s">
-        <v>463</v>
-      </c>
-      <c r="L59" t="s">
-        <v>462</v>
-      </c>
-      <c r="M59" t="s">
-        <v>464</v>
+        <v>414</v>
+      </c>
+      <c r="L59" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="M59" s="3" t="s">
+        <v>416</v>
       </c>
     </row>
     <row r="60" spans="1:13" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>138</v>
+        <v>427</v>
       </c>
       <c r="B60" t="s">
-        <v>135</v>
+        <v>94</v>
       </c>
       <c r="C60" t="s">
         <v>73</v>
@@ -29126,147 +29234,147 @@
         <v>275</v>
       </c>
       <c r="G60">
-        <v>0.89</v>
+        <v>0.84</v>
       </c>
       <c r="H60" t="s">
         <v>17</v>
       </c>
       <c r="I60" t="s">
-        <v>139</v>
+        <v>428</v>
       </c>
       <c r="J60" t="s">
-        <v>139</v>
+        <v>428</v>
       </c>
       <c r="K60" s="3" t="s">
-        <v>465</v>
-      </c>
-      <c r="L60" t="s">
-        <v>466</v>
-      </c>
-      <c r="M60" t="s">
-        <v>467</v>
+        <v>414</v>
+      </c>
+      <c r="L60" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="M60" s="3" t="s">
+        <v>430</v>
       </c>
     </row>
     <row r="61" spans="1:13" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>138</v>
+        <v>437</v>
       </c>
       <c r="B61" t="s">
-        <v>135</v>
+        <v>94</v>
       </c>
       <c r="C61" t="s">
+        <v>73</v>
+      </c>
+      <c r="D61" t="s">
         <v>15</v>
-      </c>
-      <c r="D61" t="s">
-        <v>16</v>
       </c>
       <c r="E61" t="s">
         <v>275</v>
       </c>
       <c r="G61">
-        <v>0.89</v>
+        <v>0.84</v>
       </c>
       <c r="H61" t="s">
         <v>17</v>
       </c>
       <c r="I61" t="s">
-        <v>139</v>
+        <v>438</v>
       </c>
       <c r="J61" t="s">
-        <v>139</v>
+        <v>438</v>
       </c>
       <c r="K61" s="3" t="s">
-        <v>468</v>
-      </c>
-      <c r="L61" t="s">
-        <v>467</v>
-      </c>
-      <c r="M61" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="62" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+        <v>414</v>
+      </c>
+      <c r="L61" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="M61" s="3" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>138</v>
+        <v>343</v>
       </c>
       <c r="B62" t="s">
-        <v>135</v>
+        <v>14</v>
       </c>
       <c r="C62" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="D62" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="E62" t="s">
         <v>275</v>
       </c>
       <c r="G62">
-        <v>0.99</v>
+        <v>0.85</v>
       </c>
       <c r="H62" t="s">
         <v>17</v>
       </c>
       <c r="I62" t="s">
-        <v>469</v>
+        <v>345</v>
       </c>
       <c r="J62" t="s">
-        <v>469</v>
+        <v>345</v>
       </c>
       <c r="K62" s="3" t="s">
-        <v>470</v>
-      </c>
-      <c r="L62" t="s">
-        <v>471</v>
-      </c>
-      <c r="M62" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="63" spans="1:13" ht="100.8" x14ac:dyDescent="0.3">
+        <v>352</v>
+      </c>
+      <c r="L62" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="M62" s="3" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13" ht="244.8" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>138</v>
+        <v>116</v>
       </c>
       <c r="B63" t="s">
-        <v>135</v>
+        <v>117</v>
       </c>
       <c r="C63" t="s">
-        <v>30</v>
+        <v>447</v>
       </c>
       <c r="D63" t="s">
-        <v>51</v>
+        <v>448</v>
       </c>
       <c r="E63" t="s">
         <v>275</v>
       </c>
       <c r="G63">
-        <v>0.71</v>
+        <v>0.86</v>
       </c>
       <c r="H63" t="s">
         <v>17</v>
       </c>
       <c r="I63" t="s">
-        <v>473</v>
+        <v>449</v>
       </c>
       <c r="J63" t="s">
-        <v>473</v>
+        <v>449</v>
       </c>
       <c r="K63" s="3" t="s">
-        <v>474</v>
-      </c>
-      <c r="L63" t="s">
-        <v>475</v>
-      </c>
-      <c r="M63" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="64" spans="1:13" ht="273.60000000000002" x14ac:dyDescent="0.3">
+        <v>450</v>
+      </c>
+      <c r="L63" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="M63" s="3" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" ht="244.8" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>141</v>
+        <v>119</v>
       </c>
       <c r="B64" t="s">
-        <v>135</v>
+        <v>117</v>
       </c>
       <c r="C64" t="s">
         <v>447</v>
@@ -29278,299 +29386,299 @@
         <v>275</v>
       </c>
       <c r="G64">
-        <v>0.74</v>
+        <v>0.86</v>
       </c>
       <c r="H64" t="s">
         <v>17</v>
       </c>
       <c r="I64" t="s">
-        <v>477</v>
+        <v>453</v>
       </c>
       <c r="J64" t="s">
-        <v>477</v>
+        <v>453</v>
       </c>
       <c r="K64" s="3" t="s">
-        <v>478</v>
-      </c>
-      <c r="L64" t="s">
-        <v>479</v>
-      </c>
-      <c r="M64" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="65" spans="1:13" ht="409.6" x14ac:dyDescent="0.3">
+        <v>450</v>
+      </c>
+      <c r="L64" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="M64" s="3" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13" ht="331.2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>481</v>
+        <v>40</v>
       </c>
       <c r="B65" t="s">
-        <v>135</v>
+        <v>14</v>
       </c>
       <c r="C65" t="s">
-        <v>447</v>
+        <v>33</v>
       </c>
       <c r="D65" t="s">
-        <v>448</v>
+        <v>35</v>
       </c>
       <c r="E65" t="s">
         <v>275</v>
       </c>
       <c r="G65">
-        <v>0.65</v>
+        <v>0.88</v>
       </c>
       <c r="H65" t="s">
         <v>17</v>
       </c>
       <c r="I65" t="s">
-        <v>482</v>
+        <v>46</v>
       </c>
       <c r="J65" t="s">
-        <v>482</v>
+        <v>46</v>
       </c>
       <c r="K65" s="3" t="s">
-        <v>483</v>
-      </c>
-      <c r="L65" t="s">
-        <v>484</v>
-      </c>
-      <c r="M65" t="s">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="66" spans="1:13" ht="409.6" x14ac:dyDescent="0.3">
+        <v>284</v>
+      </c>
+      <c r="L65" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="M65" s="3" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>486</v>
+        <v>138</v>
       </c>
       <c r="B66" t="s">
         <v>135</v>
       </c>
       <c r="C66" t="s">
-        <v>447</v>
+        <v>73</v>
       </c>
       <c r="D66" t="s">
-        <v>448</v>
+        <v>15</v>
       </c>
       <c r="E66" t="s">
         <v>275</v>
       </c>
       <c r="G66">
-        <v>0.65</v>
+        <v>0.89</v>
       </c>
       <c r="H66" t="s">
         <v>17</v>
       </c>
       <c r="I66" t="s">
-        <v>487</v>
+        <v>139</v>
       </c>
       <c r="J66" t="s">
-        <v>487</v>
+        <v>139</v>
       </c>
       <c r="K66" s="3" t="s">
-        <v>483</v>
-      </c>
-      <c r="L66" t="s">
-        <v>484</v>
-      </c>
-      <c r="M66" t="s">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="67" spans="1:13" ht="409.6" x14ac:dyDescent="0.3">
+        <v>465</v>
+      </c>
+      <c r="L66" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="M66" s="3" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>488</v>
+        <v>138</v>
       </c>
       <c r="B67" t="s">
         <v>135</v>
       </c>
       <c r="C67" t="s">
-        <v>447</v>
+        <v>15</v>
       </c>
       <c r="D67" t="s">
-        <v>448</v>
+        <v>16</v>
       </c>
       <c r="E67" t="s">
         <v>275</v>
       </c>
       <c r="G67">
-        <v>0.65</v>
+        <v>0.89</v>
       </c>
       <c r="H67" t="s">
         <v>17</v>
       </c>
       <c r="I67" t="s">
-        <v>489</v>
+        <v>139</v>
       </c>
       <c r="J67" t="s">
-        <v>489</v>
+        <v>139</v>
       </c>
       <c r="K67" s="3" t="s">
-        <v>483</v>
-      </c>
-      <c r="L67" t="s">
-        <v>484</v>
-      </c>
-      <c r="M67" t="s">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="68" spans="1:13" ht="409.6" x14ac:dyDescent="0.3">
+        <v>468</v>
+      </c>
+      <c r="L67" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="M67" s="3" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>490</v>
+        <v>498</v>
       </c>
       <c r="B68" t="s">
         <v>135</v>
       </c>
       <c r="C68" t="s">
-        <v>447</v>
+        <v>73</v>
       </c>
       <c r="D68" t="s">
-        <v>448</v>
+        <v>15</v>
       </c>
       <c r="E68" t="s">
         <v>275</v>
       </c>
       <c r="G68">
-        <v>0.65</v>
+        <v>0.89</v>
       </c>
       <c r="H68" t="s">
         <v>17</v>
       </c>
       <c r="I68" t="s">
-        <v>491</v>
+        <v>499</v>
       </c>
       <c r="J68" t="s">
-        <v>491</v>
+        <v>499</v>
       </c>
       <c r="K68" s="3" t="s">
-        <v>483</v>
-      </c>
-      <c r="L68" t="s">
-        <v>484</v>
-      </c>
-      <c r="M68" t="s">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="69" spans="1:13" ht="409.6" x14ac:dyDescent="0.3">
+        <v>500</v>
+      </c>
+      <c r="L68" s="3" t="s">
+        <v>501</v>
+      </c>
+      <c r="M68" s="3" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="69" spans="1:13" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>492</v>
+        <v>417</v>
       </c>
       <c r="B69" t="s">
-        <v>135</v>
+        <v>94</v>
       </c>
       <c r="C69" t="s">
-        <v>447</v>
+        <v>73</v>
       </c>
       <c r="D69" t="s">
-        <v>448</v>
+        <v>15</v>
       </c>
       <c r="E69" t="s">
         <v>275</v>
       </c>
       <c r="G69">
-        <v>0.65</v>
+        <v>0.9</v>
       </c>
       <c r="H69" t="s">
         <v>17</v>
       </c>
       <c r="I69" t="s">
-        <v>493</v>
+        <v>418</v>
       </c>
       <c r="J69" t="s">
-        <v>493</v>
+        <v>418</v>
       </c>
       <c r="K69" s="3" t="s">
-        <v>483</v>
-      </c>
-      <c r="L69" t="s">
-        <v>484</v>
-      </c>
-      <c r="M69" t="s">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="70" spans="1:13" ht="409.6" x14ac:dyDescent="0.3">
+        <v>419</v>
+      </c>
+      <c r="L69" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="M69" s="3" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="70" spans="1:13" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>494</v>
+        <v>431</v>
       </c>
       <c r="B70" t="s">
-        <v>135</v>
+        <v>94</v>
       </c>
       <c r="C70" t="s">
-        <v>447</v>
+        <v>73</v>
       </c>
       <c r="D70" t="s">
-        <v>448</v>
+        <v>15</v>
       </c>
       <c r="E70" t="s">
         <v>275</v>
       </c>
       <c r="G70">
-        <v>0.65</v>
+        <v>0.9</v>
       </c>
       <c r="H70" t="s">
         <v>17</v>
       </c>
       <c r="I70" t="s">
-        <v>495</v>
+        <v>432</v>
       </c>
       <c r="J70" t="s">
-        <v>495</v>
+        <v>432</v>
       </c>
       <c r="K70" s="3" t="s">
-        <v>483</v>
-      </c>
-      <c r="L70" t="s">
-        <v>484</v>
-      </c>
-      <c r="M70" t="s">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="71" spans="1:13" ht="409.6" x14ac:dyDescent="0.3">
+        <v>419</v>
+      </c>
+      <c r="L70" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="M70" s="3" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="71" spans="1:13" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>496</v>
+        <v>439</v>
       </c>
       <c r="B71" t="s">
-        <v>135</v>
+        <v>94</v>
       </c>
       <c r="C71" t="s">
-        <v>447</v>
+        <v>73</v>
       </c>
       <c r="D71" t="s">
-        <v>448</v>
+        <v>15</v>
       </c>
       <c r="E71" t="s">
         <v>275</v>
       </c>
       <c r="G71">
-        <v>0.65</v>
+        <v>0.9</v>
       </c>
       <c r="H71" t="s">
         <v>17</v>
       </c>
       <c r="I71" t="s">
-        <v>497</v>
+        <v>440</v>
       </c>
       <c r="J71" t="s">
-        <v>497</v>
+        <v>440</v>
       </c>
       <c r="K71" s="3" t="s">
-        <v>483</v>
-      </c>
-      <c r="L71" t="s">
-        <v>484</v>
-      </c>
-      <c r="M71" t="s">
-        <v>485</v>
+        <v>419</v>
+      </c>
+      <c r="L71" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="M71" s="3" t="s">
+        <v>421</v>
       </c>
     </row>
     <row r="72" spans="1:13" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>498</v>
+        <v>116</v>
       </c>
       <c r="B72" t="s">
-        <v>135</v>
+        <v>117</v>
       </c>
       <c r="C72" t="s">
         <v>73</v>
@@ -29582,942 +29690,942 @@
         <v>275</v>
       </c>
       <c r="G72">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="H72" t="s">
         <v>17</v>
       </c>
       <c r="I72" t="s">
-        <v>499</v>
+        <v>443</v>
       </c>
       <c r="J72" t="s">
-        <v>499</v>
+        <v>443</v>
       </c>
       <c r="K72" s="3" t="s">
-        <v>500</v>
-      </c>
-      <c r="L72" t="s">
-        <v>501</v>
-      </c>
-      <c r="M72" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="73" spans="1:13" ht="100.8" x14ac:dyDescent="0.3">
+        <v>444</v>
+      </c>
+      <c r="L72" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="M72" s="3" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="73" spans="1:13" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>152</v>
+        <v>433</v>
       </c>
       <c r="B73" t="s">
-        <v>153</v>
+        <v>94</v>
       </c>
       <c r="C73" t="s">
-        <v>28</v>
+        <v>73</v>
       </c>
       <c r="D73" t="s">
-        <v>44</v>
+        <v>15</v>
       </c>
       <c r="E73" t="s">
         <v>275</v>
       </c>
       <c r="G73">
-        <v>0.49</v>
+        <v>0.91</v>
       </c>
       <c r="H73" t="s">
         <v>17</v>
       </c>
       <c r="I73" t="s">
-        <v>154</v>
+        <v>434</v>
       </c>
       <c r="J73" t="s">
-        <v>154</v>
+        <v>434</v>
       </c>
       <c r="K73" s="3" t="s">
-        <v>503</v>
-      </c>
-      <c r="L73" t="s">
-        <v>504</v>
-      </c>
-      <c r="M73" t="s">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="74" spans="1:13" ht="409.6" x14ac:dyDescent="0.3">
+        <v>424</v>
+      </c>
+      <c r="L73" s="3" t="s">
+        <v>435</v>
+      </c>
+      <c r="M73" s="3" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="74" spans="1:13" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>152</v>
+        <v>567</v>
       </c>
       <c r="B74" t="s">
-        <v>153</v>
+        <v>218</v>
       </c>
       <c r="C74" t="s">
-        <v>447</v>
+        <v>73</v>
       </c>
       <c r="D74" t="s">
-        <v>448</v>
+        <v>15</v>
       </c>
       <c r="E74" t="s">
         <v>275</v>
       </c>
       <c r="G74">
-        <v>0.73</v>
+        <v>0.91</v>
       </c>
       <c r="H74" t="s">
         <v>17</v>
       </c>
       <c r="I74" t="s">
-        <v>487</v>
+        <v>568</v>
       </c>
       <c r="J74" t="s">
-        <v>487</v>
+        <v>568</v>
       </c>
       <c r="K74" s="3" t="s">
-        <v>506</v>
-      </c>
-      <c r="L74" t="s">
-        <v>507</v>
-      </c>
-      <c r="M74" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="75" spans="1:13" ht="409.6" x14ac:dyDescent="0.3">
+        <v>569</v>
+      </c>
+      <c r="L74" s="3" t="s">
+        <v>570</v>
+      </c>
+      <c r="M74" s="3" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="75" spans="1:13" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>509</v>
+        <v>572</v>
       </c>
       <c r="B75" t="s">
-        <v>153</v>
+        <v>218</v>
       </c>
       <c r="C75" t="s">
-        <v>447</v>
+        <v>73</v>
       </c>
       <c r="D75" t="s">
-        <v>448</v>
+        <v>15</v>
       </c>
       <c r="E75" t="s">
         <v>275</v>
       </c>
       <c r="G75">
-        <v>0.73</v>
+        <v>0.91</v>
       </c>
       <c r="H75" t="s">
         <v>17</v>
       </c>
       <c r="I75" t="s">
-        <v>495</v>
+        <v>573</v>
       </c>
       <c r="J75" t="s">
-        <v>495</v>
+        <v>573</v>
       </c>
       <c r="K75" s="3" t="s">
-        <v>506</v>
-      </c>
-      <c r="L75" t="s">
-        <v>507</v>
-      </c>
-      <c r="M75" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="76" spans="1:13" ht="409.6" x14ac:dyDescent="0.3">
+        <v>569</v>
+      </c>
+      <c r="L75" s="3" t="s">
+        <v>570</v>
+      </c>
+      <c r="M75" s="3" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="76" spans="1:13" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>510</v>
+        <v>422</v>
       </c>
       <c r="B76" t="s">
-        <v>153</v>
+        <v>94</v>
       </c>
       <c r="C76" t="s">
-        <v>447</v>
+        <v>73</v>
       </c>
       <c r="D76" t="s">
-        <v>448</v>
+        <v>15</v>
       </c>
       <c r="E76" t="s">
         <v>275</v>
       </c>
       <c r="G76">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="H76" t="s">
         <v>17</v>
       </c>
       <c r="I76" t="s">
-        <v>493</v>
+        <v>423</v>
       </c>
       <c r="J76" t="s">
-        <v>493</v>
+        <v>423</v>
       </c>
       <c r="K76" s="3" t="s">
-        <v>506</v>
-      </c>
-      <c r="L76" t="s">
-        <v>507</v>
-      </c>
-      <c r="M76" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="77" spans="1:13" ht="409.6" x14ac:dyDescent="0.3">
+        <v>424</v>
+      </c>
+      <c r="L76" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="M76" s="3" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="77" spans="1:13" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>511</v>
+        <v>441</v>
       </c>
       <c r="B77" t="s">
-        <v>153</v>
+        <v>94</v>
       </c>
       <c r="C77" t="s">
-        <v>447</v>
+        <v>73</v>
       </c>
       <c r="D77" t="s">
-        <v>448</v>
+        <v>15</v>
       </c>
       <c r="E77" t="s">
         <v>275</v>
       </c>
       <c r="G77">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="H77" t="s">
         <v>17</v>
       </c>
       <c r="I77" t="s">
-        <v>491</v>
+        <v>442</v>
       </c>
       <c r="J77" t="s">
-        <v>491</v>
+        <v>442</v>
       </c>
       <c r="K77" s="3" t="s">
-        <v>506</v>
-      </c>
-      <c r="L77" t="s">
-        <v>507</v>
-      </c>
-      <c r="M77" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="78" spans="1:13" ht="409.6" x14ac:dyDescent="0.3">
+        <v>424</v>
+      </c>
+      <c r="L77" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="M77" s="3" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="78" spans="1:13" ht="216" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>512</v>
+        <v>47</v>
       </c>
       <c r="B78" t="s">
-        <v>153</v>
+        <v>14</v>
       </c>
       <c r="C78" t="s">
-        <v>447</v>
+        <v>73</v>
       </c>
       <c r="D78" t="s">
-        <v>448</v>
+        <v>15</v>
       </c>
       <c r="E78" t="s">
         <v>275</v>
       </c>
       <c r="G78">
-        <v>0.73</v>
+        <v>0.93</v>
       </c>
       <c r="H78" t="s">
         <v>17</v>
       </c>
       <c r="I78" t="s">
-        <v>489</v>
+        <v>48</v>
       </c>
       <c r="J78" t="s">
-        <v>489</v>
+        <v>48</v>
       </c>
       <c r="K78" s="3" t="s">
-        <v>506</v>
-      </c>
-      <c r="L78" t="s">
-        <v>507</v>
-      </c>
-      <c r="M78" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="79" spans="1:13" ht="409.6" x14ac:dyDescent="0.3">
+        <v>287</v>
+      </c>
+      <c r="L78" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="M78" s="3" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="79" spans="1:13" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>513</v>
+        <v>586</v>
       </c>
       <c r="B79" t="s">
-        <v>153</v>
+        <v>218</v>
       </c>
       <c r="C79" t="s">
-        <v>447</v>
+        <v>15</v>
       </c>
       <c r="D79" t="s">
-        <v>448</v>
+        <v>16</v>
       </c>
       <c r="E79" t="s">
         <v>275</v>
       </c>
       <c r="G79">
-        <v>0.73</v>
+        <v>0.93</v>
       </c>
       <c r="H79" t="s">
         <v>17</v>
       </c>
       <c r="I79" t="s">
-        <v>497</v>
+        <v>587</v>
       </c>
       <c r="J79" t="s">
-        <v>497</v>
+        <v>587</v>
       </c>
       <c r="K79" s="3" t="s">
-        <v>506</v>
-      </c>
-      <c r="L79" t="s">
-        <v>507</v>
-      </c>
-      <c r="M79" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="80" spans="1:13" ht="100.8" x14ac:dyDescent="0.3">
+        <v>588</v>
+      </c>
+      <c r="L79" s="3" t="s">
+        <v>589</v>
+      </c>
+      <c r="M79" s="3" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="80" spans="1:13" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>157</v>
+        <v>128</v>
       </c>
       <c r="B80" t="s">
-        <v>153</v>
+        <v>117</v>
       </c>
       <c r="C80" t="s">
-        <v>28</v>
+        <v>73</v>
       </c>
       <c r="D80" t="s">
-        <v>44</v>
+        <v>15</v>
       </c>
       <c r="E80" t="s">
         <v>275</v>
       </c>
       <c r="G80">
-        <v>0.49</v>
+        <v>0.94</v>
       </c>
       <c r="H80" t="s">
         <v>17</v>
       </c>
       <c r="I80" t="s">
-        <v>158</v>
+        <v>454</v>
       </c>
       <c r="J80" t="s">
-        <v>158</v>
+        <v>454</v>
       </c>
       <c r="K80" s="3" t="s">
-        <v>503</v>
-      </c>
-      <c r="L80" t="s">
-        <v>504</v>
-      </c>
-      <c r="M80" t="s">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="81" spans="1:13" ht="100.8" x14ac:dyDescent="0.3">
+        <v>455</v>
+      </c>
+      <c r="L80" s="3" t="s">
+        <v>456</v>
+      </c>
+      <c r="M80" s="3" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="81" spans="1:13" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>157</v>
+        <v>128</v>
       </c>
       <c r="B81" t="s">
-        <v>153</v>
+        <v>117</v>
       </c>
       <c r="C81" t="s">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="D81" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="E81" t="s">
         <v>275</v>
       </c>
       <c r="G81">
-        <v>0.79</v>
+        <v>0.94</v>
       </c>
       <c r="H81" t="s">
         <v>17</v>
       </c>
       <c r="I81" t="s">
-        <v>158</v>
+        <v>454</v>
       </c>
       <c r="J81" t="s">
-        <v>158</v>
+        <v>454</v>
       </c>
       <c r="K81" s="3" t="s">
-        <v>514</v>
-      </c>
-      <c r="L81" t="s">
-        <v>505</v>
-      </c>
-      <c r="M81" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="82" spans="1:13" ht="100.8" x14ac:dyDescent="0.3">
+        <v>458</v>
+      </c>
+      <c r="L81" s="3" t="s">
+        <v>457</v>
+      </c>
+      <c r="M81" s="3" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="82" spans="1:13" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>165</v>
+        <v>522</v>
       </c>
       <c r="B82" t="s">
         <v>153</v>
       </c>
       <c r="C82" t="s">
-        <v>28</v>
+        <v>73</v>
       </c>
       <c r="D82" t="s">
-        <v>44</v>
+        <v>15</v>
       </c>
       <c r="E82" t="s">
         <v>275</v>
       </c>
       <c r="G82">
-        <v>0.49</v>
+        <v>0.94</v>
       </c>
       <c r="H82" t="s">
         <v>17</v>
       </c>
       <c r="I82" t="s">
-        <v>166</v>
+        <v>523</v>
       </c>
       <c r="J82" t="s">
-        <v>166</v>
+        <v>523</v>
       </c>
       <c r="K82" s="3" t="s">
-        <v>503</v>
-      </c>
-      <c r="L82" t="s">
-        <v>504</v>
-      </c>
-      <c r="M82" t="s">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="83" spans="1:13" ht="409.6" x14ac:dyDescent="0.3">
+        <v>524</v>
+      </c>
+      <c r="L82" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="M82" s="3" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="83" spans="1:13" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>516</v>
+        <v>69</v>
       </c>
       <c r="B83" t="s">
-        <v>153</v>
+        <v>14</v>
       </c>
       <c r="C83" t="s">
-        <v>447</v>
+        <v>73</v>
       </c>
       <c r="D83" t="s">
-        <v>448</v>
+        <v>15</v>
       </c>
       <c r="E83" t="s">
         <v>275</v>
       </c>
       <c r="G83">
-        <v>0.73</v>
+        <v>0.95</v>
       </c>
       <c r="H83" t="s">
         <v>17</v>
       </c>
       <c r="I83" t="s">
-        <v>517</v>
+        <v>327</v>
       </c>
       <c r="J83" t="s">
-        <v>517</v>
+        <v>327</v>
       </c>
       <c r="K83" s="3" t="s">
-        <v>506</v>
-      </c>
-      <c r="L83" t="s">
-        <v>507</v>
-      </c>
-      <c r="M83" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="84" spans="1:13" ht="100.8" x14ac:dyDescent="0.3">
+        <v>328</v>
+      </c>
+      <c r="L83" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="M83" s="3" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="84" spans="1:13" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>169</v>
+        <v>69</v>
       </c>
       <c r="B84" t="s">
-        <v>153</v>
+        <v>14</v>
       </c>
       <c r="C84" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="D84" t="s">
-        <v>44</v>
+        <v>16</v>
       </c>
       <c r="E84" t="s">
         <v>275</v>
       </c>
       <c r="G84">
-        <v>0.49</v>
+        <v>0.95</v>
       </c>
       <c r="H84" t="s">
         <v>17</v>
       </c>
       <c r="I84" t="s">
-        <v>170</v>
+        <v>327</v>
       </c>
       <c r="J84" t="s">
-        <v>170</v>
+        <v>327</v>
       </c>
       <c r="K84" s="3" t="s">
-        <v>503</v>
-      </c>
-      <c r="L84" t="s">
-        <v>504</v>
-      </c>
-      <c r="M84" t="s">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="85" spans="1:13" ht="100.8" x14ac:dyDescent="0.3">
+        <v>331</v>
+      </c>
+      <c r="L84" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="M84" s="3" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="85" spans="1:13" ht="288" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>171</v>
+        <v>217</v>
       </c>
       <c r="B85" t="s">
-        <v>153</v>
+        <v>218</v>
       </c>
       <c r="C85" t="s">
-        <v>28</v>
+        <v>447</v>
       </c>
       <c r="D85" t="s">
-        <v>44</v>
+        <v>448</v>
       </c>
       <c r="E85" t="s">
         <v>275</v>
       </c>
       <c r="G85">
-        <v>0.49</v>
+        <v>0.95</v>
       </c>
       <c r="H85" t="s">
         <v>17</v>
       </c>
       <c r="I85" t="s">
-        <v>172</v>
+        <v>547</v>
       </c>
       <c r="J85" t="s">
-        <v>172</v>
+        <v>547</v>
       </c>
       <c r="K85" s="3" t="s">
-        <v>503</v>
-      </c>
-      <c r="L85" t="s">
-        <v>504</v>
-      </c>
-      <c r="M85" t="s">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="86" spans="1:13" ht="100.8" x14ac:dyDescent="0.3">
+        <v>548</v>
+      </c>
+      <c r="L85" s="3" t="s">
+        <v>549</v>
+      </c>
+      <c r="M85" s="3" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="86" spans="1:13" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>171</v>
+        <v>65</v>
       </c>
       <c r="B86" t="s">
-        <v>153</v>
+        <v>14</v>
       </c>
       <c r="C86" t="s">
-        <v>45</v>
+        <v>73</v>
       </c>
       <c r="D86" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="E86" t="s">
         <v>275</v>
       </c>
       <c r="G86">
-        <v>0.79</v>
+        <v>0.96</v>
       </c>
       <c r="H86" t="s">
         <v>17</v>
       </c>
       <c r="I86" t="s">
-        <v>172</v>
+        <v>66</v>
       </c>
       <c r="J86" t="s">
-        <v>172</v>
+        <v>66</v>
       </c>
       <c r="K86" s="3" t="s">
-        <v>514</v>
-      </c>
-      <c r="L86" t="s">
-        <v>505</v>
-      </c>
-      <c r="M86" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="87" spans="1:13" ht="100.8" x14ac:dyDescent="0.3">
+        <v>312</v>
+      </c>
+      <c r="L86" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="M86" s="3" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="87" spans="1:13" ht="230.4" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>177</v>
+        <v>381</v>
       </c>
       <c r="B87" t="s">
-        <v>153</v>
+        <v>14</v>
       </c>
       <c r="C87" t="s">
-        <v>28</v>
+        <v>73</v>
       </c>
       <c r="D87" t="s">
-        <v>44</v>
+        <v>15</v>
       </c>
       <c r="E87" t="s">
         <v>275</v>
       </c>
       <c r="G87">
-        <v>0.49</v>
+        <v>0.96</v>
       </c>
       <c r="H87" t="s">
         <v>17</v>
       </c>
       <c r="I87" t="s">
-        <v>178</v>
+        <v>382</v>
       </c>
       <c r="J87" t="s">
-        <v>178</v>
+        <v>382</v>
       </c>
       <c r="K87" s="3" t="s">
-        <v>503</v>
-      </c>
-      <c r="L87" t="s">
-        <v>504</v>
-      </c>
-      <c r="M87" t="s">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="88" spans="1:13" ht="409.6" x14ac:dyDescent="0.3">
+        <v>383</v>
+      </c>
+      <c r="L87" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="M87" s="3" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="88" spans="1:13" ht="230.4" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>518</v>
+        <v>388</v>
       </c>
       <c r="B88" t="s">
-        <v>153</v>
+        <v>14</v>
       </c>
       <c r="C88" t="s">
-        <v>447</v>
+        <v>73</v>
       </c>
       <c r="D88" t="s">
-        <v>448</v>
+        <v>15</v>
       </c>
       <c r="E88" t="s">
         <v>275</v>
       </c>
       <c r="G88">
-        <v>0.73</v>
+        <v>0.96</v>
       </c>
       <c r="H88" t="s">
         <v>17</v>
       </c>
       <c r="I88" t="s">
-        <v>519</v>
+        <v>389</v>
       </c>
       <c r="J88" t="s">
-        <v>519</v>
+        <v>389</v>
       </c>
       <c r="K88" s="3" t="s">
-        <v>506</v>
-      </c>
-      <c r="L88" t="s">
-        <v>507</v>
-      </c>
-      <c r="M88" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="89" spans="1:13" ht="409.6" x14ac:dyDescent="0.3">
+        <v>390</v>
+      </c>
+      <c r="L88" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="M88" s="3" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="89" spans="1:13" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>520</v>
+        <v>79</v>
       </c>
       <c r="B89" t="s">
-        <v>153</v>
+        <v>14</v>
       </c>
       <c r="C89" t="s">
-        <v>447</v>
+        <v>27</v>
       </c>
       <c r="D89" t="s">
-        <v>448</v>
+        <v>28</v>
       </c>
       <c r="E89" t="s">
         <v>275</v>
       </c>
       <c r="G89">
-        <v>0.73</v>
+        <v>0.97</v>
       </c>
       <c r="H89" t="s">
         <v>17</v>
       </c>
       <c r="I89" t="s">
-        <v>521</v>
+        <v>365</v>
       </c>
       <c r="J89" t="s">
-        <v>521</v>
+        <v>365</v>
       </c>
       <c r="K89" s="3" t="s">
-        <v>506</v>
-      </c>
-      <c r="L89" t="s">
-        <v>507</v>
-      </c>
-      <c r="M89" t="s">
-        <v>508</v>
+        <v>366</v>
+      </c>
+      <c r="L89" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="M89" s="3" t="s">
+        <v>368</v>
       </c>
     </row>
     <row r="90" spans="1:13" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>179</v>
+        <v>217</v>
       </c>
       <c r="B90" t="s">
-        <v>153</v>
+        <v>218</v>
       </c>
       <c r="C90" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="D90" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="E90" t="s">
         <v>275</v>
       </c>
       <c r="G90">
-        <v>0.49</v>
+        <v>0.97</v>
       </c>
       <c r="H90" t="s">
         <v>17</v>
       </c>
       <c r="I90" t="s">
-        <v>180</v>
+        <v>219</v>
       </c>
       <c r="J90" t="s">
-        <v>180</v>
+        <v>219</v>
       </c>
       <c r="K90" s="3" t="s">
-        <v>503</v>
-      </c>
-      <c r="L90" t="s">
-        <v>504</v>
-      </c>
-      <c r="M90" t="s">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="91" spans="1:13" ht="100.8" x14ac:dyDescent="0.3">
+        <v>544</v>
+      </c>
+      <c r="L90" s="3" t="s">
+        <v>545</v>
+      </c>
+      <c r="M90" s="3" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="91" spans="1:13" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>179</v>
+        <v>40</v>
       </c>
       <c r="B91" t="s">
-        <v>153</v>
+        <v>14</v>
       </c>
       <c r="C91" t="s">
-        <v>45</v>
+        <v>73</v>
       </c>
       <c r="D91" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="E91" t="s">
         <v>275</v>
       </c>
       <c r="G91">
-        <v>0.79</v>
+        <v>0.98</v>
       </c>
       <c r="H91" t="s">
         <v>17</v>
       </c>
       <c r="I91" t="s">
-        <v>180</v>
+        <v>276</v>
       </c>
       <c r="J91" t="s">
-        <v>180</v>
+        <v>276</v>
       </c>
       <c r="K91" s="3" t="s">
-        <v>514</v>
-      </c>
-      <c r="L91" t="s">
-        <v>505</v>
-      </c>
-      <c r="M91" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="92" spans="1:13" ht="187.2" x14ac:dyDescent="0.3">
+        <v>277</v>
+      </c>
+      <c r="L91" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="M91" s="3" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="92" spans="1:13" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>522</v>
+        <v>40</v>
       </c>
       <c r="B92" t="s">
-        <v>153</v>
+        <v>14</v>
       </c>
       <c r="C92" t="s">
-        <v>73</v>
+        <v>15</v>
       </c>
       <c r="D92" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E92" t="s">
         <v>275</v>
       </c>
       <c r="G92">
-        <v>0.94</v>
+        <v>0.98</v>
       </c>
       <c r="H92" t="s">
         <v>17</v>
       </c>
       <c r="I92" t="s">
-        <v>523</v>
+        <v>276</v>
       </c>
       <c r="J92" t="s">
-        <v>523</v>
+        <v>276</v>
       </c>
       <c r="K92" s="3" t="s">
-        <v>524</v>
-      </c>
-      <c r="L92" t="s">
-        <v>525</v>
-      </c>
-      <c r="M92" t="s">
-        <v>526</v>
-      </c>
-    </row>
-    <row r="93" spans="1:13" ht="129.6" x14ac:dyDescent="0.3">
+        <v>280</v>
+      </c>
+      <c r="L92" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="M92" s="3" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="93" spans="1:13" ht="216" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>205</v>
+        <v>67</v>
       </c>
       <c r="B93" t="s">
-        <v>191</v>
+        <v>14</v>
       </c>
       <c r="C93" t="s">
-        <v>30</v>
+        <v>73</v>
       </c>
       <c r="D93" t="s">
-        <v>51</v>
+        <v>15</v>
       </c>
       <c r="E93" t="s">
         <v>275</v>
       </c>
       <c r="G93">
-        <v>0.49</v>
+        <v>0.98</v>
       </c>
       <c r="H93" t="s">
         <v>17</v>
       </c>
       <c r="I93" t="s">
-        <v>527</v>
+        <v>68</v>
       </c>
       <c r="J93" t="s">
-        <v>527</v>
+        <v>68</v>
       </c>
       <c r="K93" s="3" t="s">
-        <v>528</v>
-      </c>
-      <c r="L93" t="s">
-        <v>529</v>
-      </c>
-      <c r="M93" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="94" spans="1:13" ht="129.6" x14ac:dyDescent="0.3">
+        <v>315</v>
+      </c>
+      <c r="L93" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="M93" s="3" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="94" spans="1:13" ht="72" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>531</v>
+        <v>376</v>
       </c>
       <c r="B94" t="s">
-        <v>191</v>
+        <v>14</v>
       </c>
       <c r="C94" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="D94" t="s">
-        <v>51</v>
+        <v>24</v>
       </c>
       <c r="E94" t="s">
         <v>275</v>
       </c>
       <c r="G94">
-        <v>0.47</v>
+        <v>0.98</v>
       </c>
       <c r="H94" t="s">
         <v>17</v>
       </c>
       <c r="I94" t="s">
-        <v>532</v>
+        <v>377</v>
       </c>
       <c r="J94" t="s">
-        <v>532</v>
+        <v>377</v>
       </c>
       <c r="K94" s="3" t="s">
-        <v>533</v>
-      </c>
-      <c r="L94" t="s">
-        <v>534</v>
-      </c>
-      <c r="M94" t="s">
-        <v>535</v>
-      </c>
-    </row>
-    <row r="95" spans="1:13" ht="129.6" x14ac:dyDescent="0.3">
+        <v>378</v>
+      </c>
+      <c r="L94" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="M94" s="3" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="95" spans="1:13" ht="72" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>536</v>
+        <v>376</v>
       </c>
       <c r="B95" t="s">
-        <v>191</v>
+        <v>14</v>
       </c>
       <c r="C95" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="D95" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="E95" t="s">
         <v>275</v>
       </c>
       <c r="G95">
-        <v>0.47</v>
+        <v>0.98</v>
       </c>
       <c r="H95" t="s">
         <v>17</v>
       </c>
       <c r="I95" t="s">
-        <v>537</v>
+        <v>377</v>
       </c>
       <c r="J95" t="s">
-        <v>537</v>
+        <v>377</v>
       </c>
       <c r="K95" s="3" t="s">
-        <v>533</v>
-      </c>
-      <c r="L95" t="s">
-        <v>534</v>
-      </c>
-      <c r="M95" t="s">
-        <v>535</v>
-      </c>
-    </row>
-    <row r="96" spans="1:13" ht="129.6" x14ac:dyDescent="0.3">
+        <v>380</v>
+      </c>
+      <c r="L95" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="M95" s="3" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="96" spans="1:13" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>538</v>
+        <v>217</v>
       </c>
       <c r="B96" t="s">
-        <v>191</v>
+        <v>218</v>
       </c>
       <c r="C96" t="s">
-        <v>30</v>
+        <v>73</v>
       </c>
       <c r="D96" t="s">
-        <v>51</v>
+        <v>15</v>
       </c>
       <c r="E96" t="s">
         <v>275</v>
       </c>
       <c r="G96">
-        <v>0.47</v>
+        <v>0.98</v>
       </c>
       <c r="H96" t="s">
         <v>17</v>
       </c>
       <c r="I96" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="J96" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="K96" s="3" t="s">
-        <v>533</v>
-      </c>
-      <c r="L96" t="s">
-        <v>534</v>
-      </c>
-      <c r="M96" t="s">
-        <v>535</v>
-      </c>
-    </row>
-    <row r="97" spans="1:13" ht="100.8" x14ac:dyDescent="0.3">
+        <v>541</v>
+      </c>
+      <c r="L96" s="3" t="s">
+        <v>542</v>
+      </c>
+      <c r="M96" s="3" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="97" spans="1:13" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>217</v>
+        <v>239</v>
       </c>
       <c r="B97" t="s">
         <v>218</v>
@@ -30538,100 +30646,100 @@
         <v>17</v>
       </c>
       <c r="I97" t="s">
-        <v>540</v>
+        <v>554</v>
       </c>
       <c r="J97" t="s">
-        <v>540</v>
+        <v>554</v>
       </c>
       <c r="K97" s="3" t="s">
-        <v>541</v>
-      </c>
-      <c r="L97" t="s">
-        <v>542</v>
-      </c>
-      <c r="M97" t="s">
-        <v>543</v>
-      </c>
-    </row>
-    <row r="98" spans="1:13" ht="100.8" x14ac:dyDescent="0.3">
+        <v>555</v>
+      </c>
+      <c r="L97" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="M97" s="3" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="98" spans="1:13" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>217</v>
+        <v>574</v>
       </c>
       <c r="B98" t="s">
         <v>218</v>
       </c>
       <c r="C98" t="s">
-        <v>45</v>
+        <v>73</v>
       </c>
       <c r="D98" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="E98" t="s">
         <v>275</v>
       </c>
       <c r="G98">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="H98" t="s">
         <v>17</v>
       </c>
       <c r="I98" t="s">
-        <v>219</v>
+        <v>575</v>
       </c>
       <c r="J98" t="s">
-        <v>219</v>
+        <v>575</v>
       </c>
       <c r="K98" s="3" t="s">
-        <v>544</v>
-      </c>
-      <c r="L98" t="s">
-        <v>545</v>
-      </c>
-      <c r="M98" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="99" spans="1:13" ht="244.8" x14ac:dyDescent="0.3">
+        <v>555</v>
+      </c>
+      <c r="L98" s="3" t="s">
+        <v>576</v>
+      </c>
+      <c r="M98" s="3" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="99" spans="1:13" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>217</v>
+        <v>578</v>
       </c>
       <c r="B99" t="s">
         <v>218</v>
       </c>
       <c r="C99" t="s">
-        <v>447</v>
+        <v>73</v>
       </c>
       <c r="D99" t="s">
-        <v>448</v>
+        <v>15</v>
       </c>
       <c r="E99" t="s">
         <v>275</v>
       </c>
       <c r="G99">
-        <v>0.95</v>
+        <v>0.98</v>
       </c>
       <c r="H99" t="s">
         <v>17</v>
       </c>
       <c r="I99" t="s">
-        <v>547</v>
+        <v>579</v>
       </c>
       <c r="J99" t="s">
-        <v>547</v>
+        <v>579</v>
       </c>
       <c r="K99" s="3" t="s">
-        <v>548</v>
-      </c>
-      <c r="L99" t="s">
-        <v>549</v>
-      </c>
-      <c r="M99" t="s">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="100" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+        <v>580</v>
+      </c>
+      <c r="L99" s="3" t="s">
+        <v>581</v>
+      </c>
+      <c r="M99" s="3" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="100" spans="1:13" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>235</v>
+        <v>257</v>
       </c>
       <c r="B100" t="s">
         <v>218</v>
@@ -30646,185 +30754,185 @@
         <v>275</v>
       </c>
       <c r="G100">
-        <v>0.99</v>
+        <v>0.98</v>
       </c>
       <c r="H100" t="s">
         <v>17</v>
       </c>
       <c r="I100" t="s">
-        <v>236</v>
+        <v>258</v>
       </c>
       <c r="J100" t="s">
-        <v>236</v>
+        <v>258</v>
       </c>
       <c r="K100" s="3" t="s">
-        <v>551</v>
-      </c>
-      <c r="L100" t="s">
-        <v>552</v>
-      </c>
-      <c r="M100" t="s">
-        <v>553</v>
-      </c>
-    </row>
-    <row r="101" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+        <v>583</v>
+      </c>
+      <c r="L100" s="3" t="s">
+        <v>584</v>
+      </c>
+      <c r="M100" s="3" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="101" spans="1:13" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>239</v>
+        <v>75</v>
       </c>
       <c r="B101" t="s">
-        <v>218</v>
+        <v>14</v>
       </c>
       <c r="C101" t="s">
-        <v>73</v>
+        <v>15</v>
       </c>
       <c r="D101" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E101" t="s">
         <v>275</v>
       </c>
       <c r="G101">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="H101" t="s">
         <v>17</v>
       </c>
       <c r="I101" t="s">
-        <v>554</v>
+        <v>76</v>
       </c>
       <c r="J101" t="s">
-        <v>554</v>
+        <v>76</v>
       </c>
       <c r="K101" s="3" t="s">
-        <v>555</v>
-      </c>
-      <c r="L101" t="s">
-        <v>556</v>
-      </c>
-      <c r="M101" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="102" spans="1:13" ht="409.6" x14ac:dyDescent="0.3">
+        <v>340</v>
+      </c>
+      <c r="L101" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="M101" s="3" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="102" spans="1:13" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>239</v>
+        <v>343</v>
       </c>
       <c r="B102" t="s">
-        <v>218</v>
+        <v>14</v>
       </c>
       <c r="C102" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="D102" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="E102" t="s">
         <v>275</v>
       </c>
       <c r="G102">
-        <v>0.5</v>
+        <v>0.99</v>
       </c>
       <c r="H102" t="s">
         <v>17</v>
       </c>
       <c r="I102" t="s">
-        <v>558</v>
+        <v>345</v>
       </c>
       <c r="J102" t="s">
-        <v>558</v>
+        <v>345</v>
       </c>
       <c r="K102" s="3" t="s">
-        <v>559</v>
-      </c>
-      <c r="L102" t="s">
-        <v>560</v>
-      </c>
-      <c r="M102" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="103" spans="1:13" ht="302.39999999999998" x14ac:dyDescent="0.3">
+        <v>349</v>
+      </c>
+      <c r="L102" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="M102" s="3" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="103" spans="1:13" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>562</v>
+        <v>381</v>
       </c>
       <c r="B103" t="s">
-        <v>218</v>
+        <v>14</v>
       </c>
       <c r="C103" t="s">
-        <v>447</v>
+        <v>15</v>
       </c>
       <c r="D103" t="s">
-        <v>448</v>
+        <v>16</v>
       </c>
       <c r="E103" t="s">
         <v>275</v>
       </c>
       <c r="G103">
-        <v>0.83</v>
+        <v>0.99</v>
       </c>
       <c r="H103" t="s">
         <v>17</v>
       </c>
       <c r="I103" t="s">
-        <v>563</v>
+        <v>382</v>
       </c>
       <c r="J103" t="s">
-        <v>563</v>
+        <v>382</v>
       </c>
       <c r="K103" s="3" t="s">
-        <v>564</v>
-      </c>
-      <c r="L103" t="s">
-        <v>565</v>
-      </c>
-      <c r="M103" t="s">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="104" spans="1:13" ht="129.6" x14ac:dyDescent="0.3">
+        <v>386</v>
+      </c>
+      <c r="L103" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="M103" s="3" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="104" spans="1:13" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>567</v>
+        <v>388</v>
       </c>
       <c r="B104" t="s">
-        <v>218</v>
+        <v>14</v>
       </c>
       <c r="C104" t="s">
-        <v>73</v>
+        <v>15</v>
       </c>
       <c r="D104" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E104" t="s">
         <v>275</v>
       </c>
       <c r="G104">
-        <v>0.91</v>
+        <v>0.99</v>
       </c>
       <c r="H104" t="s">
         <v>17</v>
       </c>
       <c r="I104" t="s">
-        <v>568</v>
+        <v>389</v>
       </c>
       <c r="J104" t="s">
-        <v>568</v>
+        <v>389</v>
       </c>
       <c r="K104" s="3" t="s">
-        <v>569</v>
-      </c>
-      <c r="L104" t="s">
-        <v>570</v>
-      </c>
-      <c r="M104" t="s">
-        <v>571</v>
-      </c>
-    </row>
-    <row r="105" spans="1:13" ht="129.6" x14ac:dyDescent="0.3">
+        <v>386</v>
+      </c>
+      <c r="L104" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="M104" s="3" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="105" spans="1:13" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>572</v>
+        <v>394</v>
       </c>
       <c r="B105" t="s">
-        <v>218</v>
+        <v>14</v>
       </c>
       <c r="C105" t="s">
         <v>73</v>
@@ -30836,71 +30944,71 @@
         <v>275</v>
       </c>
       <c r="G105">
-        <v>0.91</v>
+        <v>0.99</v>
       </c>
       <c r="H105" t="s">
         <v>17</v>
       </c>
       <c r="I105" t="s">
-        <v>573</v>
+        <v>395</v>
       </c>
       <c r="J105" t="s">
-        <v>573</v>
+        <v>395</v>
       </c>
       <c r="K105" s="3" t="s">
-        <v>569</v>
-      </c>
-      <c r="L105" t="s">
-        <v>570</v>
-      </c>
-      <c r="M105" t="s">
-        <v>571</v>
+        <v>396</v>
+      </c>
+      <c r="L105" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="M105" s="3" t="s">
+        <v>398</v>
       </c>
     </row>
     <row r="106" spans="1:13" ht="72" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>574</v>
+        <v>394</v>
       </c>
       <c r="B106" t="s">
-        <v>218</v>
+        <v>14</v>
       </c>
       <c r="C106" t="s">
-        <v>73</v>
+        <v>15</v>
       </c>
       <c r="D106" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E106" t="s">
         <v>275</v>
       </c>
       <c r="G106">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="H106" t="s">
         <v>17</v>
       </c>
       <c r="I106" t="s">
-        <v>575</v>
+        <v>395</v>
       </c>
       <c r="J106" t="s">
-        <v>575</v>
+        <v>395</v>
       </c>
       <c r="K106" s="3" t="s">
-        <v>555</v>
-      </c>
-      <c r="L106" t="s">
-        <v>576</v>
-      </c>
-      <c r="M106" t="s">
-        <v>577</v>
-      </c>
-    </row>
-    <row r="107" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+        <v>399</v>
+      </c>
+      <c r="L106" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="M106" s="3" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="107" spans="1:13" ht="144" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>578</v>
+        <v>100</v>
       </c>
       <c r="B107" t="s">
-        <v>218</v>
+        <v>94</v>
       </c>
       <c r="C107" t="s">
         <v>73</v>
@@ -30912,105 +31020,108 @@
         <v>275</v>
       </c>
       <c r="G107">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="H107" t="s">
         <v>17</v>
       </c>
       <c r="I107" t="s">
-        <v>579</v>
+        <v>408</v>
       </c>
       <c r="J107" t="s">
-        <v>579</v>
+        <v>408</v>
       </c>
       <c r="K107" s="3" t="s">
-        <v>580</v>
-      </c>
-      <c r="L107" t="s">
-        <v>581</v>
-      </c>
-      <c r="M107" t="s">
-        <v>582</v>
+        <v>409</v>
+      </c>
+      <c r="L107" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="M107" s="3" t="s">
+        <v>411</v>
       </c>
     </row>
     <row r="108" spans="1:13" ht="72" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>257</v>
+        <v>138</v>
       </c>
       <c r="B108" t="s">
-        <v>218</v>
+        <v>135</v>
       </c>
       <c r="C108" t="s">
-        <v>73</v>
+        <v>27</v>
       </c>
       <c r="D108" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="E108" t="s">
         <v>275</v>
       </c>
       <c r="G108">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="H108" t="s">
         <v>17</v>
       </c>
       <c r="I108" t="s">
-        <v>258</v>
+        <v>469</v>
       </c>
       <c r="J108" t="s">
-        <v>258</v>
+        <v>469</v>
       </c>
       <c r="K108" s="3" t="s">
-        <v>583</v>
-      </c>
-      <c r="L108" t="s">
-        <v>584</v>
-      </c>
-      <c r="M108" t="s">
-        <v>585</v>
-      </c>
-    </row>
-    <row r="109" spans="1:13" ht="129.6" x14ac:dyDescent="0.3">
+        <v>470</v>
+      </c>
+      <c r="L108" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="M108" s="3" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="109" spans="1:13" ht="144" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>586</v>
+        <v>235</v>
       </c>
       <c r="B109" t="s">
         <v>218</v>
       </c>
       <c r="C109" t="s">
+        <v>73</v>
+      </c>
+      <c r="D109" t="s">
         <v>15</v>
-      </c>
-      <c r="D109" t="s">
-        <v>16</v>
       </c>
       <c r="E109" t="s">
         <v>275</v>
       </c>
       <c r="G109">
-        <v>0.93</v>
+        <v>0.99</v>
       </c>
       <c r="H109" t="s">
         <v>17</v>
       </c>
       <c r="I109" t="s">
-        <v>587</v>
+        <v>236</v>
       </c>
       <c r="J109" t="s">
-        <v>587</v>
+        <v>236</v>
       </c>
       <c r="K109" s="3" t="s">
-        <v>588</v>
-      </c>
-      <c r="L109" t="s">
-        <v>589</v>
-      </c>
-      <c r="M109" t="s">
-        <v>590</v>
+        <v>551</v>
+      </c>
+      <c r="L109" s="3" t="s">
+        <v>552</v>
+      </c>
+      <c r="M109" s="3" t="s">
+        <v>553</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
@@ -31020,6 +31131,7 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="8" max="8" width="51" style="3" customWidth="1"/>
+    <col min="11" max="11" width="9.88671875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
